--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37BAB451-7E25-4505-9D98-EBC61F80B589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6111FD8F-2E51-49B6-8A66-30D65143FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -618,8 +618,12 @@
       <c r="G1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
+      <c r="H1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
@@ -677,6 +681,12 @@
       <c r="G2" s="2">
         <v>45706</v>
       </c>
+      <c r="H2" s="2">
+        <v>45707</v>
+      </c>
+      <c r="I2" s="2">
+        <v>45713</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -705,6 +715,12 @@
       <c r="G4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -728,6 +744,12 @@
       <c r="G5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -751,6 +773,12 @@
       <c r="G6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -774,6 +802,12 @@
       <c r="G7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -797,6 +831,12 @@
       <c r="G8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -820,6 +860,12 @@
       <c r="G9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -843,6 +889,12 @@
       <c r="G10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -866,6 +918,12 @@
       <c r="G11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -889,6 +947,12 @@
       <c r="G12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -912,6 +976,12 @@
       <c r="G13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -935,6 +1005,12 @@
       <c r="G14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -958,6 +1034,12 @@
       <c r="G15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -981,6 +1063,12 @@
       <c r="G16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1004,6 +1092,12 @@
       <c r="G17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1027,6 +1121,12 @@
       <c r="G18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1050,6 +1150,12 @@
       <c r="G19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1073,6 +1179,12 @@
       <c r="G20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
@@ -1102,6 +1214,12 @@
       <c r="G22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1125,6 +1243,12 @@
       <c r="G23" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1148,6 +1272,12 @@
       <c r="G24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1171,6 +1301,12 @@
       <c r="G25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1194,6 +1330,12 @@
       <c r="G26" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="H26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1217,6 +1359,12 @@
       <c r="G27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I27" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
     </row>
@@ -1242,6 +1390,12 @@
       <c r="G28" s="1" t="s">
         <v>42</v>
       </c>
+      <c r="H28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1265,6 +1419,12 @@
       <c r="G29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1288,6 +1448,12 @@
       <c r="G30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1311,6 +1477,12 @@
       <c r="G31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="H31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1334,8 +1506,14 @@
       <c r="G32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -1357,8 +1535,14 @@
       <c r="G33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -1380,8 +1564,14 @@
       <c r="G34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -1403,8 +1593,14 @@
       <c r="G35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -1426,8 +1622,14 @@
       <c r="G36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -1447,6 +1649,12 @@
         <v>3</v>
       </c>
       <c r="G37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6111FD8F-2E51-49B6-8A66-30D65143FA43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4836FE11-B6D0-4E09-A1A6-5898C12692FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -624,7 +624,9 @@
       <c r="I1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="2"/>
+      <c r="J1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -687,6 +689,9 @@
       <c r="I2" s="2">
         <v>45713</v>
       </c>
+      <c r="J2" s="2">
+        <v>45714</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -1220,6 +1225,9 @@
       <c r="I22" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="J22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1249,6 +1257,9 @@
       <c r="I23" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J23" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1278,6 +1289,9 @@
       <c r="I24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1307,6 +1321,9 @@
       <c r="I25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1336,6 +1353,9 @@
       <c r="I26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1365,6 +1385,9 @@
       <c r="I27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J27" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
     </row>
@@ -1396,6 +1419,9 @@
       <c r="I28" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1425,6 +1451,9 @@
       <c r="I29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1454,6 +1483,9 @@
       <c r="I30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1483,6 +1515,9 @@
       <c r="I31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1512,8 +1547,11 @@
       <c r="I32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -1541,8 +1579,11 @@
       <c r="I33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -1570,8 +1611,11 @@
       <c r="I34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -1599,8 +1643,11 @@
       <c r="I35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -1628,8 +1675,11 @@
       <c r="I36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="J36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -1656,6 +1706,9 @@
       </c>
       <c r="I37" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="J37" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\ds\3des\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellington\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4836FE11-B6D0-4E09-A1A6-5898C12692FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20983BC3-E141-45A4-A3AF-9F7F274162A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="195" yWindow="0" windowWidth="14250" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -726,6 +726,9 @@
       <c r="I4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -755,6 +758,9 @@
       <c r="I5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -784,6 +790,9 @@
       <c r="I6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -813,6 +822,9 @@
       <c r="I7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -842,6 +854,9 @@
       <c r="I8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -871,6 +886,9 @@
       <c r="I9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -900,6 +918,9 @@
       <c r="I10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -929,6 +950,9 @@
       <c r="I11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -958,6 +982,9 @@
       <c r="I12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -987,6 +1014,9 @@
       <c r="I13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1016,6 +1046,9 @@
       <c r="I14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1045,6 +1078,9 @@
       <c r="I15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1074,6 +1110,9 @@
       <c r="I16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1103,6 +1142,9 @@
       <c r="I17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1132,6 +1174,9 @@
       <c r="I18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1161,6 +1206,9 @@
       <c r="I19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="J19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1188,6 +1236,9 @@
         <v>3</v>
       </c>
       <c r="I20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellington\senai2025\ds\3des\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20983BC3-E141-45A4-A3AF-9F7F274162A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96273C71-EAAD-411A-904F-D5FA9FB31E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="195" yWindow="0" windowWidth="14250" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -627,7 +627,9 @@
       <c r="J1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="2"/>
+      <c r="K1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -692,6 +694,9 @@
       <c r="J2" s="2">
         <v>45714</v>
       </c>
+      <c r="K2" s="2">
+        <v>45727</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -729,6 +734,9 @@
       <c r="J4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -761,6 +769,9 @@
       <c r="J5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -793,6 +804,9 @@
       <c r="J6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -825,6 +839,9 @@
       <c r="J7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -857,6 +874,9 @@
       <c r="J8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -889,6 +909,9 @@
       <c r="J9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K9" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -921,6 +944,9 @@
       <c r="J10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -953,6 +979,9 @@
       <c r="J11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -985,6 +1014,9 @@
       <c r="J12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1017,6 +1049,9 @@
       <c r="J13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1049,6 +1084,9 @@
       <c r="J14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1081,6 +1119,9 @@
       <c r="J15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1113,6 +1154,9 @@
       <c r="J16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1145,6 +1189,9 @@
       <c r="J17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1177,6 +1224,9 @@
       <c r="J18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1209,6 +1259,9 @@
       <c r="J19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1241,6 +1294,9 @@
       <c r="J20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
@@ -1279,6 +1335,9 @@
       <c r="J22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1311,6 +1370,9 @@
       <c r="J23" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K23" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1343,6 +1405,9 @@
       <c r="J24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1375,6 +1440,9 @@
       <c r="J25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1407,6 +1475,9 @@
       <c r="J26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1439,6 +1510,9 @@
       <c r="J27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K27" s="1" t="s">
+        <v>3</v>
+      </c>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
     </row>
@@ -1473,6 +1547,9 @@
       <c r="J28" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1505,6 +1582,9 @@
       <c r="J29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1537,6 +1617,9 @@
       <c r="J30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1569,6 +1652,9 @@
       <c r="J31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="K31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1601,8 +1687,11 @@
       <c r="J32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -1633,8 +1722,11 @@
       <c r="J33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -1665,8 +1757,11 @@
       <c r="J34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -1697,8 +1792,11 @@
       <c r="J35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -1729,8 +1827,11 @@
       <c r="J36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="K36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -1760,6 +1861,9 @@
       </c>
       <c r="J37" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="K37" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellington\senai2025\ds\3des\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96273C71-EAAD-411A-904F-D5FA9FB31E71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929BAEFF-7883-47E4-8CF3-A82ECC1785B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="344" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -630,7 +630,9 @@
       <c r="K1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="2"/>
+      <c r="L1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
@@ -697,6 +699,9 @@
       <c r="K2" s="2">
         <v>45727</v>
       </c>
+      <c r="L2" s="2">
+        <v>45728</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -737,6 +742,9 @@
       <c r="K4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -772,6 +780,9 @@
       <c r="K5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -807,6 +818,9 @@
       <c r="K6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -842,6 +856,9 @@
       <c r="K7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -877,6 +894,9 @@
       <c r="K8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -912,6 +932,9 @@
       <c r="K9" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="L9" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -947,6 +970,9 @@
       <c r="K10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -982,6 +1008,9 @@
       <c r="K11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1017,6 +1046,9 @@
       <c r="K12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1052,6 +1084,9 @@
       <c r="K13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1087,6 +1122,9 @@
       <c r="K14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1122,6 +1160,9 @@
       <c r="K15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1157,6 +1198,9 @@
       <c r="K16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
@@ -1192,6 +1236,9 @@
       <c r="K17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
@@ -1227,6 +1274,9 @@
       <c r="K18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
@@ -1262,6 +1312,9 @@
       <c r="K19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
@@ -1297,6 +1350,9 @@
       <c r="K20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
@@ -1338,6 +1394,9 @@
       <c r="K22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
@@ -1373,6 +1432,9 @@
       <c r="K23" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L23" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
@@ -1408,6 +1470,9 @@
       <c r="K24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
@@ -1443,6 +1508,9 @@
       <c r="K25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
@@ -1478,6 +1546,9 @@
       <c r="K26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="27" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
@@ -1513,7 +1584,9 @@
       <c r="K27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="6"/>
+      <c r="L27" s="6" t="s">
+        <v>3</v>
+      </c>
       <c r="M27" s="6"/>
     </row>
     <row r="28" spans="1:13" x14ac:dyDescent="0.25">
@@ -1550,6 +1623,9 @@
       <c r="K28" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="29" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
@@ -1585,6 +1661,9 @@
       <c r="K29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="30" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
@@ -1620,6 +1699,9 @@
       <c r="K30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="31" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
@@ -1655,6 +1737,9 @@
       <c r="K31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="L31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="32" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
@@ -1690,8 +1775,11 @@
       <c r="K32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -1725,8 +1813,11 @@
       <c r="K33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -1760,8 +1851,11 @@
       <c r="K34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -1795,8 +1889,11 @@
       <c r="K35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -1830,8 +1927,11 @@
       <c r="K36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -1863,6 +1963,9 @@
         <v>4</v>
       </c>
       <c r="K37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="L37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{929BAEFF-7883-47E4-8CF3-A82ECC1785B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB6DB9-C168-4B2C-9FAC-C201704A438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -160,7 +160,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -180,6 +180,12 @@
       <u/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -211,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +238,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -633,8 +642,12 @@
       <c r="L1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="2"/>
-      <c r="N1" s="2"/>
+      <c r="M1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
       <c r="Q1" s="2"/>
@@ -702,6 +715,12 @@
       <c r="L2" s="2">
         <v>45728</v>
       </c>
+      <c r="M2" s="2">
+        <v>45734</v>
+      </c>
+      <c r="N2" s="2">
+        <v>45735</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -745,6 +764,12 @@
       <c r="L4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -783,6 +808,12 @@
       <c r="L5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -821,6 +852,12 @@
       <c r="L6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -859,6 +896,12 @@
       <c r="L7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -897,6 +940,12 @@
       <c r="L8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -935,6 +984,12 @@
       <c r="L9" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="M9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -973,6 +1028,12 @@
       <c r="L10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1011,6 +1072,12 @@
       <c r="L11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1049,6 +1116,12 @@
       <c r="L12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1087,6 +1160,12 @@
       <c r="L13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1125,6 +1204,12 @@
       <c r="L14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1163,6 +1248,12 @@
       <c r="L15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="M15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1201,8 +1292,14 @@
       <c r="L16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1239,8 +1336,14 @@
       <c r="L17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1277,8 +1380,14 @@
       <c r="L18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1315,8 +1424,14 @@
       <c r="L19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1353,14 +1468,20 @@
       <c r="L20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="M20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1397,8 +1518,14 @@
       <c r="L22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1435,8 +1562,14 @@
       <c r="L23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -1473,8 +1606,14 @@
       <c r="L24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1511,8 +1650,14 @@
       <c r="L25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1549,8 +1694,14 @@
       <c r="L26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -1584,12 +1735,17 @@
       <c r="K27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="6"/>
-    </row>
-    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="L27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>3</v>
+      </c>
+      <c r="N27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -1626,8 +1782,14 @@
       <c r="L28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -1664,8 +1826,14 @@
       <c r="L29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -1702,8 +1870,14 @@
       <c r="L30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N30" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -1740,8 +1914,14 @@
       <c r="L31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -1778,8 +1958,14 @@
       <c r="L32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -1816,8 +2002,14 @@
       <c r="L33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -1854,8 +2046,14 @@
       <c r="L34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -1892,8 +2090,14 @@
       <c r="L35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -1930,8 +2134,14 @@
       <c r="L36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -1966,6 +2176,12 @@
         <v>3</v>
       </c>
       <c r="L37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="N37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1976,6 +2192,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
     <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"F"</formula>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\ds\3des\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BFB6DB9-C168-4B2C-9FAC-C201704A438E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A964C-6DDD-4616-A4E3-DB604163AFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="446" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -217,7 +217,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -238,9 +238,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -590,14 +587,9 @@
     <col min="2" max="2" width="3.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.7109375" style="1"/>
-    <col min="6" max="6" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="18" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="10" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="22" max="23" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
@@ -648,8 +640,12 @@
       <c r="N1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="2"/>
-      <c r="P1" s="2"/>
+      <c r="O1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="Q1" s="2"/>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
@@ -721,6 +717,12 @@
       <c r="N2" s="2">
         <v>45735</v>
       </c>
+      <c r="O2" s="2">
+        <v>45741</v>
+      </c>
+      <c r="P2" s="2">
+        <v>45742</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -1735,10 +1737,10 @@
       <c r="K27" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="L27" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="M27" s="8" t="s">
+      <c r="L27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M27" s="1" t="s">
         <v>3</v>
       </c>
       <c r="N27" s="1" t="s">

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sn1057928\Desktop\senai2025\ds\3des\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476A964C-6DDD-4616-A4E3-DB604163AFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D94DBF7-0589-44AB-9163-028AF03DA042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -772,6 +772,9 @@
       <c r="N4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -816,6 +819,9 @@
       <c r="N5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -860,6 +866,9 @@
       <c r="N6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -904,6 +913,9 @@
       <c r="N7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -948,6 +960,9 @@
       <c r="N8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -992,6 +1007,9 @@
       <c r="N9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1036,6 +1054,9 @@
       <c r="N10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1080,6 +1101,9 @@
       <c r="N11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1124,6 +1148,9 @@
       <c r="N12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1168,6 +1195,9 @@
       <c r="N13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1212,6 +1242,9 @@
       <c r="N14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1256,6 +1289,9 @@
       <c r="N15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="O15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1300,8 +1336,11 @@
       <c r="N16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1344,8 +1383,11 @@
       <c r="N17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1388,8 +1430,11 @@
       <c r="N18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1432,8 +1477,11 @@
       <c r="N19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1476,14 +1524,17 @@
       <c r="N20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="O20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1526,8 +1577,11 @@
       <c r="N22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1570,8 +1624,11 @@
       <c r="N23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -1614,8 +1671,11 @@
       <c r="N24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1658,8 +1718,11 @@
       <c r="N25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1702,8 +1765,11 @@
       <c r="N26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -1746,8 +1812,11 @@
       <c r="N27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -1790,8 +1859,11 @@
       <c r="N28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -1834,8 +1906,11 @@
       <c r="N29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -1878,8 +1953,11 @@
       <c r="N30" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -1922,8 +2000,11 @@
       <c r="N31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -1966,8 +2047,11 @@
       <c r="N32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2010,8 +2094,11 @@
       <c r="N33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2054,8 +2141,11 @@
       <c r="N34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2098,8 +2188,11 @@
       <c r="N35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2142,8 +2235,11 @@
       <c r="N36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2184,6 +2280,9 @@
         <v>3</v>
       </c>
       <c r="N37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D94DBF7-0589-44AB-9163-028AF03DA042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A598ED-0A00-4A20-9CD1-53B89C4C74BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="481" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="43">
   <si>
     <t>Alunos</t>
   </si>
@@ -646,7 +646,9 @@
       <c r="P1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="2"/>
+      <c r="Q1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
@@ -723,6 +725,9 @@
       <c r="P2" s="2">
         <v>45742</v>
       </c>
+      <c r="Q2" s="2">
+        <v>45748</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -775,6 +780,12 @@
       <c r="O4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -822,6 +833,12 @@
       <c r="O5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -869,6 +886,12 @@
       <c r="O6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -916,6 +939,12 @@
       <c r="O7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -963,6 +992,12 @@
       <c r="O8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1010,6 +1045,12 @@
       <c r="O9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1057,6 +1098,12 @@
       <c r="O10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1104,6 +1151,12 @@
       <c r="O11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1151,6 +1204,12 @@
       <c r="O12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1198,6 +1257,12 @@
       <c r="O13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1245,6 +1310,12 @@
       <c r="O14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1292,6 +1363,12 @@
       <c r="O15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="P15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1339,8 +1416,14 @@
       <c r="O16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1386,8 +1469,14 @@
       <c r="O17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1433,8 +1522,14 @@
       <c r="O18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1480,8 +1575,14 @@
       <c r="O19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1527,14 +1628,20 @@
       <c r="O20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:15" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1580,8 +1687,14 @@
       <c r="O22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1627,8 +1740,14 @@
       <c r="O23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -1674,8 +1793,14 @@
       <c r="O24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1721,8 +1846,14 @@
       <c r="O25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1768,8 +1899,14 @@
       <c r="O26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -1815,8 +1952,14 @@
       <c r="O27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -1862,8 +2005,14 @@
       <c r="O28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -1909,8 +2058,14 @@
       <c r="O29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -1956,8 +2111,14 @@
       <c r="O30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2003,8 +2164,14 @@
       <c r="O31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2050,8 +2217,14 @@
       <c r="O32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2097,8 +2270,14 @@
       <c r="O33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2144,8 +2323,14 @@
       <c r="O34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2191,8 +2376,14 @@
       <c r="O35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2238,8 +2429,14 @@
       <c r="O36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2284,6 +2481,12 @@
       </c>
       <c r="O37" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="P37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\wellifabio\senai2025\ds\3des\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A598ED-0A00-4A20-9CD1-53B89C4C74BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5DD97A-AE7A-4F4E-8057-46757F02DCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="44">
   <si>
     <t>Alunos</t>
   </si>
@@ -154,6 +154,9 @@
   </si>
   <si>
     <t>5P</t>
+  </si>
+  <si>
+    <t>P/5</t>
   </si>
 </sst>
 </file>
@@ -649,9 +652,15 @@
       <c r="Q1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="2"/>
-      <c r="S1" s="2"/>
-      <c r="T1" s="2"/>
+      <c r="R1" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
@@ -728,6 +737,15 @@
       <c r="Q2" s="2">
         <v>45748</v>
       </c>
+      <c r="R2" s="2">
+        <v>45749</v>
+      </c>
+      <c r="S2" s="2">
+        <v>45755</v>
+      </c>
+      <c r="T2" s="2">
+        <v>45756</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -786,6 +804,12 @@
       <c r="Q4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -839,6 +863,12 @@
       <c r="Q5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -892,6 +922,12 @@
       <c r="Q6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -945,6 +981,12 @@
       <c r="Q7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -998,6 +1040,12 @@
       <c r="Q8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1051,6 +1099,12 @@
       <c r="Q9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1104,6 +1158,12 @@
       <c r="Q10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1157,6 +1217,12 @@
       <c r="Q11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1210,6 +1276,12 @@
       <c r="Q12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1263,6 +1335,12 @@
       <c r="Q13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1316,6 +1394,12 @@
       <c r="Q14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1369,6 +1453,12 @@
       <c r="Q15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="R15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1422,8 +1512,14 @@
       <c r="Q16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1475,8 +1571,14 @@
       <c r="Q17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1528,8 +1630,14 @@
       <c r="Q18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1581,8 +1689,14 @@
       <c r="Q19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1634,14 +1748,20 @@
       <c r="Q20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:17" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="R20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1693,8 +1813,14 @@
       <c r="Q22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1746,8 +1872,14 @@
       <c r="Q23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -1799,8 +1931,14 @@
       <c r="Q24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1852,8 +1990,14 @@
       <c r="Q25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -1905,8 +2049,14 @@
       <c r="Q26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -1958,8 +2108,14 @@
       <c r="Q27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2011,8 +2167,14 @@
       <c r="Q28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2064,8 +2226,14 @@
       <c r="Q29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2117,8 +2285,14 @@
       <c r="Q30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2170,8 +2344,14 @@
       <c r="Q31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2223,8 +2403,14 @@
       <c r="Q32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2276,8 +2462,14 @@
       <c r="Q33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2329,8 +2521,14 @@
       <c r="Q34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2382,8 +2580,14 @@
       <c r="Q35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2435,8 +2639,14 @@
       <c r="Q36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="R36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2487,6 +2697,12 @@
       </c>
       <c r="Q37" s="1" t="s">
         <v>4</v>
+      </c>
+      <c r="R37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="S37" s="1" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B5DD97A-AE7A-4F4E-8057-46757F02DCB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEA24FD-1BE8-4EBF-B42E-D159F949CFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="617" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="44">
   <si>
     <t>Alunos</t>
   </si>
@@ -810,6 +810,9 @@
       <c r="S4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -869,6 +872,9 @@
       <c r="S5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -928,6 +934,9 @@
       <c r="S6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -987,6 +996,9 @@
       <c r="S7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1046,6 +1058,9 @@
       <c r="S8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1105,6 +1120,9 @@
       <c r="S9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1164,6 +1182,9 @@
       <c r="S10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1223,6 +1244,9 @@
       <c r="S11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1282,6 +1306,9 @@
       <c r="S12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1341,6 +1368,9 @@
       <c r="S13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1400,6 +1430,9 @@
       <c r="S14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1459,6 +1492,9 @@
       <c r="S15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="T15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1518,8 +1554,11 @@
       <c r="S16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1577,8 +1616,11 @@
       <c r="S17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1636,8 +1678,11 @@
       <c r="S18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1695,8 +1740,11 @@
       <c r="S19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1754,14 +1802,17 @@
       <c r="S20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="T20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1819,8 +1870,11 @@
       <c r="S22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1878,8 +1932,11 @@
       <c r="S23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -1937,8 +1994,11 @@
       <c r="S24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -1996,8 +2056,11 @@
       <c r="S25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2055,8 +2118,11 @@
       <c r="S26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2114,8 +2180,11 @@
       <c r="S27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2173,8 +2242,11 @@
       <c r="S28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2232,8 +2304,11 @@
       <c r="S29" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2291,8 +2366,11 @@
       <c r="S30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2350,8 +2428,11 @@
       <c r="S31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2409,8 +2490,11 @@
       <c r="S32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2468,8 +2552,11 @@
       <c r="S33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2527,8 +2614,11 @@
       <c r="S34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2586,8 +2676,11 @@
       <c r="S35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2645,8 +2738,11 @@
       <c r="S36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2703,6 +2799,9 @@
       </c>
       <c r="S37" s="1" t="s">
         <v>43</v>
+      </c>
+      <c r="T37" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBEA24FD-1BE8-4EBF-B42E-D159F949CFCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8E35B6-ECDB-4D99-9A36-A35ABB9B3665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="650" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="44">
   <si>
     <t>Alunos</t>
   </si>
@@ -661,7 +661,9 @@
       <c r="T1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="2"/>
+      <c r="U1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="V1" s="2"/>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
@@ -746,6 +748,9 @@
       <c r="T2" s="2">
         <v>45756</v>
       </c>
+      <c r="U2" s="2">
+        <v>45762</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -813,6 +818,9 @@
       <c r="T4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -875,6 +883,9 @@
       <c r="T5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -937,6 +948,9 @@
       <c r="T6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -999,6 +1013,9 @@
       <c r="T7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1061,6 +1078,9 @@
       <c r="T8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1123,6 +1143,9 @@
       <c r="T9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1185,6 +1208,9 @@
       <c r="T10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1247,6 +1273,9 @@
       <c r="T11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1309,6 +1338,9 @@
       <c r="T12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1371,6 +1403,9 @@
       <c r="T13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1433,6 +1468,9 @@
       <c r="T14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1495,6 +1533,9 @@
       <c r="T15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="U15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1557,8 +1598,11 @@
       <c r="T16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1619,8 +1663,11 @@
       <c r="T17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1681,8 +1728,11 @@
       <c r="T18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1743,8 +1793,11 @@
       <c r="T19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1805,14 +1858,17 @@
       <c r="T20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:20" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="U20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1873,8 +1929,11 @@
       <c r="T22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1935,8 +1994,11 @@
       <c r="T23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -1997,8 +2059,11 @@
       <c r="T24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2059,8 +2124,11 @@
       <c r="T25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2121,8 +2189,11 @@
       <c r="T26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2183,8 +2254,11 @@
       <c r="T27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2245,8 +2319,11 @@
       <c r="T28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2307,8 +2384,11 @@
       <c r="T29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2369,8 +2449,11 @@
       <c r="T30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2431,8 +2514,11 @@
       <c r="T31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2493,8 +2579,11 @@
       <c r="T32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2555,8 +2644,11 @@
       <c r="T33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2617,8 +2709,11 @@
       <c r="T34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2679,8 +2774,11 @@
       <c r="T35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2741,8 +2839,11 @@
       <c r="T36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2801,6 +2902,9 @@
         <v>43</v>
       </c>
       <c r="T37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC8E35B6-ECDB-4D99-9A36-A35ABB9B3665}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B21000A-B280-43D9-8726-68434E59C623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
+    <sheet name="alunos" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="152511"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="44">
   <si>
     <t>Alunos</t>
   </si>
@@ -220,7 +221,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -243,6 +244,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2932,4 +2934,191 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5601EA4F-B083-49FB-A81E-FB069AE1076F}">
+  <dimension ref="A1:A34"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" s="8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>36</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A34">
+    <sortCondition ref="A1:A34"/>
+  </sortState>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B21000A-B280-43D9-8726-68434E59C623}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6897F2-C76F-4112-867E-1C3CD28EA4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="718" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="44">
   <si>
     <t>Alunos</t>
   </si>
@@ -241,10 +241,10 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -605,10 +605,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7"/>
+      <c r="B1" s="8"/>
       <c r="C1" s="2" t="s">
         <v>39</v>
       </c>
@@ -666,7 +666,9 @@
       <c r="U1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="2"/>
+      <c r="V1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="W1" s="2"/>
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
@@ -753,6 +755,9 @@
       <c r="U2" s="2">
         <v>45762</v>
       </c>
+      <c r="V2" s="2">
+        <v>45763</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -823,6 +828,9 @@
       <c r="U4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -888,6 +896,9 @@
       <c r="U5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -953,6 +964,9 @@
       <c r="U6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1018,6 +1032,9 @@
       <c r="U7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1083,6 +1100,9 @@
       <c r="U8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1148,6 +1168,9 @@
       <c r="U9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1213,6 +1236,9 @@
       <c r="U10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1278,6 +1304,9 @@
       <c r="U11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1343,6 +1372,9 @@
       <c r="U12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1408,6 +1440,9 @@
       <c r="U13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1473,6 +1508,9 @@
       <c r="U14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1538,6 +1576,9 @@
       <c r="U15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="V15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1603,8 +1644,11 @@
       <c r="U16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1668,8 +1712,11 @@
       <c r="U17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1733,8 +1780,11 @@
       <c r="U18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1798,8 +1848,11 @@
       <c r="U19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1863,14 +1916,17 @@
       <c r="U20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:21" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="V20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1934,8 +1990,11 @@
       <c r="U22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -1999,8 +2058,11 @@
       <c r="U23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2064,8 +2126,11 @@
       <c r="U24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V24" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2129,8 +2194,11 @@
       <c r="U25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2194,8 +2262,11 @@
       <c r="U26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2259,8 +2330,11 @@
       <c r="U27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2324,8 +2398,11 @@
       <c r="U28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2389,8 +2466,11 @@
       <c r="U29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2454,8 +2534,11 @@
       <c r="U30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2519,8 +2602,11 @@
       <c r="U31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2584,8 +2670,11 @@
       <c r="U32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2649,8 +2738,11 @@
       <c r="U33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2714,8 +2806,11 @@
       <c r="U34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2779,8 +2874,11 @@
       <c r="U35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2844,8 +2942,11 @@
       <c r="U36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -2907,6 +3008,9 @@
         <v>3</v>
       </c>
       <c r="U37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -2945,7 +3049,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF6897F2-C76F-4112-867E-1C3CD28EA4C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A79DFB7-3662-40FD-AB9C-4A10795B88C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="752" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="44">
   <si>
     <t>Alunos</t>
   </si>
@@ -669,8 +669,12 @@
       <c r="V1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="2"/>
-      <c r="X1" s="2"/>
+      <c r="W1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="X1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
       <c r="AA1" s="2"/>
@@ -758,6 +762,12 @@
       <c r="V2" s="2">
         <v>45763</v>
       </c>
+      <c r="W2" s="2">
+        <v>45769</v>
+      </c>
+      <c r="X2" s="2">
+        <v>45770</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -831,6 +841,12 @@
       <c r="V4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -899,6 +915,12 @@
       <c r="V5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -967,6 +989,12 @@
       <c r="V6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1035,6 +1063,12 @@
       <c r="V7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1103,6 +1137,12 @@
       <c r="V8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1171,6 +1211,12 @@
       <c r="V9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1239,6 +1285,12 @@
       <c r="V10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1307,6 +1359,12 @@
       <c r="V11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1375,6 +1433,12 @@
       <c r="V12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1443,6 +1507,12 @@
       <c r="V13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1511,6 +1581,12 @@
       <c r="V14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1579,6 +1655,12 @@
       <c r="V15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="W15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1647,8 +1729,14 @@
       <c r="V16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1715,8 +1803,14 @@
       <c r="V17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1783,8 +1877,14 @@
       <c r="V18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1851,8 +1951,14 @@
       <c r="V19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -1919,14 +2025,20 @@
       <c r="V20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -1993,8 +2105,14 @@
       <c r="V22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2061,8 +2179,14 @@
       <c r="V23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2129,8 +2253,14 @@
       <c r="V24" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2197,8 +2327,14 @@
       <c r="V25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2265,8 +2401,14 @@
       <c r="V26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2333,8 +2475,14 @@
       <c r="V27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2401,8 +2549,14 @@
       <c r="V28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2469,8 +2623,14 @@
       <c r="V29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2537,8 +2697,14 @@
       <c r="V30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2605,8 +2771,14 @@
       <c r="V31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2673,8 +2845,14 @@
       <c r="V32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2741,8 +2919,14 @@
       <c r="V33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2809,8 +2993,14 @@
       <c r="V34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -2877,8 +3067,14 @@
       <c r="V35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -2945,8 +3141,14 @@
       <c r="V36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3011,6 +3213,12 @@
         <v>3</v>
       </c>
       <c r="V37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="W37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="X37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A79DFB7-3662-40FD-AB9C-4A10795B88C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788CB12B-2A6D-40FA-B7F6-884E8DE79241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -158,6 +158,9 @@
   </si>
   <si>
     <t>P/5</t>
+  </si>
+  <si>
+    <t>5/P</t>
   </si>
 </sst>
 </file>
@@ -675,8 +678,12 @@
       <c r="X1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y1" s="2"/>
-      <c r="Z1" s="2"/>
+      <c r="Y1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="Z1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AA1" s="2"/>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
@@ -768,6 +775,12 @@
       <c r="X2" s="2">
         <v>45770</v>
       </c>
+      <c r="Y2" s="2">
+        <v>45776</v>
+      </c>
+      <c r="Z2" s="2">
+        <v>45777</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -847,6 +860,12 @@
       <c r="X4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -921,6 +940,12 @@
       <c r="X5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -995,6 +1020,12 @@
       <c r="X6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1069,6 +1100,12 @@
       <c r="X7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1143,6 +1180,12 @@
       <c r="X8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1217,6 +1260,12 @@
       <c r="X9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1291,6 +1340,12 @@
       <c r="X10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1365,6 +1420,12 @@
       <c r="X11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1439,6 +1500,12 @@
       <c r="X12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z12" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1513,6 +1580,12 @@
       <c r="X13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1587,6 +1660,12 @@
       <c r="X14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1661,6 +1740,12 @@
       <c r="X15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="Y15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1735,8 +1820,14 @@
       <c r="X16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1809,8 +1900,14 @@
       <c r="X17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1883,8 +1980,14 @@
       <c r="X18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -1957,8 +2060,14 @@
       <c r="X19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2031,14 +2140,20 @@
       <c r="X20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:24" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2111,8 +2226,14 @@
       <c r="X22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2185,8 +2306,14 @@
       <c r="X23" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2259,8 +2386,14 @@
       <c r="X24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2333,8 +2466,14 @@
       <c r="X25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z25" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2407,8 +2546,14 @@
       <c r="X26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2481,8 +2626,14 @@
       <c r="X27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2555,8 +2706,14 @@
       <c r="X28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2629,8 +2786,14 @@
       <c r="X29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2703,8 +2866,14 @@
       <c r="X30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2777,8 +2946,14 @@
       <c r="X31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -2851,8 +3026,14 @@
       <c r="X32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -2925,8 +3106,14 @@
       <c r="X33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -2999,8 +3186,14 @@
       <c r="X34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3073,8 +3266,14 @@
       <c r="X35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y35" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3147,8 +3346,14 @@
       <c r="X36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="Y36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3219,6 +3424,12 @@
         <v>3</v>
       </c>
       <c r="X37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{788CB12B-2A6D-40FA-B7F6-884E8DE79241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1039D682-45C7-40CB-8093-CA4D9A556F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3187,7 +3187,7 @@
         <v>3</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="Z34" s="1" t="s">
         <v>3</v>
@@ -3267,7 +3267,7 @@
         <v>3</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="Z35" s="1" t="s">
         <v>3</v>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1039D682-45C7-40CB-8093-CA4D9A556F27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DAE598-9F98-41EB-83CD-F2063A916600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31DAE598-9F98-41EB-83CD-F2063A916600}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50048786-EF47-46E6-A3CF-6C530F3C8A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -684,7 +684,9 @@
       <c r="Z1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AA1" s="2"/>
+      <c r="AA1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AB1" s="2"/>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
@@ -781,6 +783,9 @@
       <c r="Z2" s="2">
         <v>45777</v>
       </c>
+      <c r="AA2" s="2">
+        <v>45783</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -866,6 +871,9 @@
       <c r="Z4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -946,6 +954,9 @@
       <c r="Z5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1026,6 +1037,9 @@
       <c r="Z6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1106,6 +1120,9 @@
       <c r="Z7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1186,6 +1203,9 @@
       <c r="Z8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1266,6 +1286,9 @@
       <c r="Z9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1346,6 +1369,9 @@
       <c r="Z10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1426,6 +1452,9 @@
       <c r="Z11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1506,6 +1535,9 @@
       <c r="Z12" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AA12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1586,6 +1618,9 @@
       <c r="Z13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1666,6 +1701,9 @@
       <c r="Z14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1746,6 +1784,9 @@
       <c r="Z15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AA15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1826,8 +1867,11 @@
       <c r="Z16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1906,8 +1950,11 @@
       <c r="Z17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -1986,8 +2033,11 @@
       <c r="Z18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2066,8 +2116,11 @@
       <c r="Z19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2146,14 +2199,17 @@
       <c r="Z20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AA20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2232,8 +2288,11 @@
       <c r="Z22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA22" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2312,8 +2371,11 @@
       <c r="Z23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA23" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2392,8 +2454,11 @@
       <c r="Z24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2472,8 +2537,11 @@
       <c r="Z25" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2552,8 +2620,11 @@
       <c r="Z26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2632,8 +2703,11 @@
       <c r="Z27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2712,8 +2786,11 @@
       <c r="Z28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2792,8 +2869,11 @@
       <c r="Z29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2872,8 +2952,11 @@
       <c r="Z30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -2952,8 +3035,11 @@
       <c r="Z31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3032,8 +3118,11 @@
       <c r="Z32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3112,8 +3201,11 @@
       <c r="Z33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3192,8 +3284,11 @@
       <c r="Z34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3272,8 +3367,11 @@
       <c r="Z35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3352,8 +3450,11 @@
       <c r="Z36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="AA36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3430,6 +3531,9 @@
         <v>3</v>
       </c>
       <c r="Z37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50048786-EF47-46E6-A3CF-6C530F3C8A68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEA075B-60F7-4ED6-9BDA-F12FCF9ADE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="922" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -687,7 +687,9 @@
       <c r="AA1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="2"/>
+      <c r="AB1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AC1" s="2"/>
       <c r="AD1" s="2"/>
       <c r="AE1" s="2"/>
@@ -786,6 +788,9 @@
       <c r="AA2" s="2">
         <v>45783</v>
       </c>
+      <c r="AB2" s="2">
+        <v>45784</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -874,6 +879,9 @@
       <c r="AA4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -957,6 +965,9 @@
       <c r="AA5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1040,6 +1051,9 @@
       <c r="AA6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1123,6 +1137,9 @@
       <c r="AA7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1206,6 +1223,9 @@
       <c r="AA8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1289,6 +1309,9 @@
       <c r="AA9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1372,6 +1395,9 @@
       <c r="AA10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1455,6 +1481,9 @@
       <c r="AA11" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AB11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1538,6 +1567,9 @@
       <c r="AA12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB12" s="1" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1621,6 +1653,9 @@
       <c r="AA13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1704,6 +1739,9 @@
       <c r="AA14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1787,6 +1825,9 @@
       <c r="AA15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AB15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1870,8 +1911,11 @@
       <c r="AA16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -1953,8 +1997,11 @@
       <c r="AA17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2036,8 +2083,11 @@
       <c r="AA18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2119,8 +2169,11 @@
       <c r="AA19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2202,14 +2255,17 @@
       <c r="AA20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:27" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AB20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:28" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2291,8 +2347,11 @@
       <c r="AA22" s="1" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2374,8 +2433,11 @@
       <c r="AA23" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB23" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2457,8 +2519,11 @@
       <c r="AA24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2540,8 +2605,11 @@
       <c r="AA25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2623,8 +2691,11 @@
       <c r="AA26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2706,8 +2777,11 @@
       <c r="AA27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2789,8 +2863,11 @@
       <c r="AA28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2872,8 +2949,11 @@
       <c r="AA29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -2955,8 +3035,11 @@
       <c r="AA30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3038,8 +3121,11 @@
       <c r="AA31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3121,8 +3207,11 @@
       <c r="AA32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3204,8 +3293,11 @@
       <c r="AA33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3287,8 +3379,11 @@
       <c r="AA34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3370,8 +3465,11 @@
       <c r="AA35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3453,8 +3551,11 @@
       <c r="AA36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="AB36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3534,6 +3635,9 @@
         <v>3</v>
       </c>
       <c r="AA37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DEA075B-60F7-4ED6-9BDA-F12FCF9ADE5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFCE819-7E5A-4E55-8114-91B642F3E56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -246,6 +246,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2501,8 +2504,8 @@
       <c r="U24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="1" t="s">
-        <v>4</v>
+      <c r="V24" s="9" t="s">
+        <v>3</v>
       </c>
       <c r="W24" s="1" t="s">
         <v>3</v>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAFCE819-7E5A-4E55-8114-91B642F3E56A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CA5562-E9CA-4CC5-9C38-7EED9A21B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="956" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -224,7 +224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -246,9 +246,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,8 +690,12 @@
       <c r="AB1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="2"/>
-      <c r="AD1" s="2"/>
+      <c r="AC1" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="AD1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AE1" s="2"/>
       <c r="AF1" s="2"/>
       <c r="AG1" s="2"/>
@@ -794,6 +795,12 @@
       <c r="AB2" s="2">
         <v>45784</v>
       </c>
+      <c r="AC2" s="2">
+        <v>45790</v>
+      </c>
+      <c r="AD2" s="2">
+        <v>45791</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -885,6 +892,12 @@
       <c r="AB4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -971,6 +984,12 @@
       <c r="AB5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD5" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1057,6 +1076,12 @@
       <c r="AB6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1143,6 +1168,12 @@
       <c r="AB7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1229,6 +1260,12 @@
       <c r="AB8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1315,6 +1352,12 @@
       <c r="AB9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1401,6 +1444,12 @@
       <c r="AB10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1487,6 +1536,12 @@
       <c r="AB11" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AC11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1573,6 +1628,12 @@
       <c r="AB12" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AC12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1659,6 +1720,12 @@
       <c r="AB13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1745,6 +1812,12 @@
       <c r="AB14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1831,6 +1904,12 @@
       <c r="AB15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AC15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -1917,8 +1996,14 @@
       <c r="AB16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2003,8 +2088,14 @@
       <c r="AB17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2089,8 +2180,14 @@
       <c r="AB18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2175,8 +2272,14 @@
       <c r="AB19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2261,14 +2364,20 @@
       <c r="AB20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:28" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AC20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2353,8 +2462,14 @@
       <c r="AB22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2439,8 +2554,14 @@
       <c r="AB23" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2504,7 +2625,7 @@
       <c r="U24" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="V24" s="9" t="s">
+      <c r="V24" s="1" t="s">
         <v>3</v>
       </c>
       <c r="W24" s="1" t="s">
@@ -2525,8 +2646,14 @@
       <c r="AB24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2611,8 +2738,14 @@
       <c r="AB25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2697,8 +2830,14 @@
       <c r="AB26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2783,8 +2922,14 @@
       <c r="AB27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -2869,8 +3014,14 @@
       <c r="AB28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC28" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -2955,8 +3106,14 @@
       <c r="AB29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3041,8 +3198,14 @@
       <c r="AB30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3127,8 +3290,14 @@
       <c r="AB31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3213,8 +3382,14 @@
       <c r="AB32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3299,8 +3474,14 @@
       <c r="AB33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3385,8 +3566,14 @@
       <c r="AB34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3471,8 +3658,14 @@
       <c r="AB35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3557,8 +3750,14 @@
       <c r="AB36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="AC36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3641,6 +3840,12 @@
         <v>3</v>
       </c>
       <c r="AB37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AD37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86CA5562-E9CA-4CC5-9C38-7EED9A21B85C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F89070-637D-4A40-B62F-28507EAF871E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -988,7 +988,7 @@
         <v>3</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67F89070-637D-4A40-B62F-28507EAF871E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445FF5C2-E179-49B0-AAF2-39F97D733418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -696,7 +696,9 @@
       <c r="AD1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AE1" s="2"/>
+      <c r="AE1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AF1" s="2"/>
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
@@ -801,6 +803,9 @@
       <c r="AD2" s="2">
         <v>45791</v>
       </c>
+      <c r="AE2" s="2">
+        <v>45797</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -898,6 +903,9 @@
       <c r="AD4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -990,6 +998,9 @@
       <c r="AD5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1082,6 +1093,9 @@
       <c r="AD6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1174,6 +1188,9 @@
       <c r="AD7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1266,6 +1283,9 @@
       <c r="AD8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1358,6 +1378,9 @@
       <c r="AD9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE9" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1450,6 +1473,9 @@
       <c r="AD10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1542,6 +1568,9 @@
       <c r="AD11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1634,6 +1663,9 @@
       <c r="AD12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1726,6 +1758,9 @@
       <c r="AD13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1818,6 +1853,9 @@
       <c r="AD14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1910,6 +1948,9 @@
       <c r="AD15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AE15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2002,8 +2043,11 @@
       <c r="AD16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2094,8 +2138,11 @@
       <c r="AD17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2186,8 +2233,11 @@
       <c r="AD18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2278,8 +2328,11 @@
       <c r="AD19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2370,14 +2423,17 @@
       <c r="AD20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:30" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AE20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2468,8 +2524,11 @@
       <c r="AD22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2560,8 +2619,11 @@
       <c r="AD23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2652,8 +2714,11 @@
       <c r="AD24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2744,8 +2809,11 @@
       <c r="AD25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2836,8 +2904,11 @@
       <c r="AD26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -2928,8 +2999,11 @@
       <c r="AD27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3020,8 +3094,11 @@
       <c r="AD28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3112,8 +3189,11 @@
       <c r="AD29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3204,8 +3284,11 @@
       <c r="AD30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3296,8 +3379,11 @@
       <c r="AD31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3388,8 +3474,11 @@
       <c r="AD32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3480,8 +3569,11 @@
       <c r="AD33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3572,8 +3664,11 @@
       <c r="AD34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3664,8 +3759,11 @@
       <c r="AD35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3756,8 +3854,11 @@
       <c r="AD36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+      <c r="AE36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3846,6 +3947,9 @@
         <v>3</v>
       </c>
       <c r="AD37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AE37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{445FF5C2-E179-49B0-AAF2-39F97D733418}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6587CD-5A5A-45CE-A509-19A1FCC2FA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1058" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -604,7 +604,8 @@
     <col min="24" max="26" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="16384" width="6.7109375" style="1"/>
+    <col min="32" max="32" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -699,7 +700,9 @@
       <c r="AE1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="2"/>
+      <c r="AF1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AG1" s="2"/>
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
@@ -806,6 +809,9 @@
       <c r="AE2" s="2">
         <v>45797</v>
       </c>
+      <c r="AF2" s="2">
+        <v>45798</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -906,6 +912,9 @@
       <c r="AE4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1001,6 +1010,9 @@
       <c r="AE5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1096,6 +1108,9 @@
       <c r="AE6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1191,6 +1206,9 @@
       <c r="AE7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1286,6 +1304,9 @@
       <c r="AE8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1381,6 +1402,9 @@
       <c r="AE9" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AF9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1476,6 +1500,9 @@
       <c r="AE10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1571,6 +1598,9 @@
       <c r="AE11" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AF11" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1666,6 +1696,9 @@
       <c r="AE12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1761,6 +1794,9 @@
       <c r="AE13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1856,6 +1892,9 @@
       <c r="AE14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1951,6 +1990,9 @@
       <c r="AE15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AF15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2046,8 +2088,11 @@
       <c r="AE16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2141,8 +2186,11 @@
       <c r="AE17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2236,8 +2284,11 @@
       <c r="AE18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2331,8 +2382,11 @@
       <c r="AE19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF19" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2426,14 +2480,17 @@
       <c r="AE20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:31" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AF20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2527,8 +2584,11 @@
       <c r="AE22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2622,8 +2682,11 @@
       <c r="AE23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2717,8 +2780,11 @@
       <c r="AE24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2812,8 +2878,11 @@
       <c r="AE25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2907,8 +2976,11 @@
       <c r="AE26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3002,8 +3074,11 @@
       <c r="AE27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3097,8 +3172,11 @@
       <c r="AE28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3192,8 +3270,11 @@
       <c r="AE29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3287,8 +3368,11 @@
       <c r="AE30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3382,8 +3466,11 @@
       <c r="AE31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3477,8 +3564,11 @@
       <c r="AE32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3572,8 +3662,11 @@
       <c r="AE33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3667,8 +3760,11 @@
       <c r="AE34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3762,8 +3858,11 @@
       <c r="AE35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3857,8 +3956,11 @@
       <c r="AE36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="AF36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -3950,6 +4052,9 @@
         <v>3</v>
       </c>
       <c r="AE37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AF37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B6587CD-5A5A-45CE-A509-19A1FCC2FA70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D60351-F7F3-42F3-A91C-71BC4BD6D433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1400,7 +1400,7 @@
         <v>3</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF9" s="1" t="s">
         <v>3</v>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D60351-F7F3-42F3-A91C-71BC4BD6D433}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F698A473-F45F-4278-B91D-A34F17A2F080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1092" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -604,8 +604,8 @@
     <col min="24" max="26" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="6.7109375" style="1"/>
+    <col min="32" max="33" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -703,7 +703,9 @@
       <c r="AF1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AG1" s="2"/>
+      <c r="AG1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AH1" s="2"/>
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
@@ -812,6 +814,9 @@
       <c r="AF2" s="2">
         <v>45798</v>
       </c>
+      <c r="AG2" s="2">
+        <v>45804</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -915,6 +920,9 @@
       <c r="AF4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1013,6 +1021,9 @@
       <c r="AF5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1111,6 +1122,9 @@
       <c r="AF6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1209,6 +1223,9 @@
       <c r="AF7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1307,6 +1324,9 @@
       <c r="AF8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1405,6 +1425,9 @@
       <c r="AF9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1503,6 +1526,9 @@
       <c r="AF10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1601,6 +1627,9 @@
       <c r="AF11" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AG11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1699,6 +1728,9 @@
       <c r="AF12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1797,6 +1829,9 @@
       <c r="AF13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1895,6 +1930,9 @@
       <c r="AF14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -1993,6 +2031,9 @@
       <c r="AF15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AG15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2091,8 +2132,11 @@
       <c r="AF16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2189,8 +2233,11 @@
       <c r="AF17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2287,8 +2334,11 @@
       <c r="AF18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2385,8 +2435,11 @@
       <c r="AF19" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2483,14 +2536,17 @@
       <c r="AF20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:32" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AG20" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2587,8 +2643,11 @@
       <c r="AF22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2685,8 +2744,11 @@
       <c r="AF23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2783,8 +2845,11 @@
       <c r="AF24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2881,8 +2946,11 @@
       <c r="AF25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -2979,8 +3047,11 @@
       <c r="AF26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3077,8 +3148,11 @@
       <c r="AF27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3175,8 +3249,11 @@
       <c r="AF28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3273,8 +3350,11 @@
       <c r="AF29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3371,8 +3451,11 @@
       <c r="AF30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3469,8 +3552,11 @@
       <c r="AF31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3567,8 +3653,11 @@
       <c r="AF32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3665,8 +3754,11 @@
       <c r="AF33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3763,8 +3855,11 @@
       <c r="AF34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3861,8 +3956,11 @@
       <c r="AF35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -3959,8 +4057,11 @@
       <c r="AF36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="AG36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -4055,6 +4156,9 @@
         <v>3</v>
       </c>
       <c r="AF37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F698A473-F45F-4278-B91D-A34F17A2F080}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677DEAD8-939E-4471-840F-C1E452BEB3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1126" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="45">
   <si>
     <t>Alunos</t>
   </si>
@@ -604,8 +604,8 @@
     <col min="24" max="26" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="27" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="6.7109375" style="1"/>
+    <col min="32" max="34" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -706,7 +706,9 @@
       <c r="AG1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AH1" s="2"/>
+      <c r="AH1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AI1" s="2"/>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
@@ -817,6 +819,9 @@
       <c r="AG2" s="2">
         <v>45804</v>
       </c>
+      <c r="AH2" s="2">
+        <v>45805</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -923,6 +928,9 @@
       <c r="AG4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1024,6 +1032,9 @@
       <c r="AG5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1125,6 +1136,9 @@
       <c r="AG6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1226,6 +1240,9 @@
       <c r="AG7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1327,6 +1344,9 @@
       <c r="AG8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1428,6 +1448,9 @@
       <c r="AG9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1529,6 +1552,9 @@
       <c r="AG10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1630,6 +1656,9 @@
       <c r="AG11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1731,6 +1760,9 @@
       <c r="AG12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH12" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1832,6 +1864,9 @@
       <c r="AG13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1933,6 +1968,9 @@
       <c r="AG14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -2034,6 +2072,9 @@
       <c r="AG15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AH15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2135,8 +2176,11 @@
       <c r="AG16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2236,8 +2280,11 @@
       <c r="AG17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2337,8 +2384,11 @@
       <c r="AG18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2438,8 +2488,11 @@
       <c r="AG19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2539,14 +2592,17 @@
       <c r="AG20" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="21" spans="1:33" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AH20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2646,8 +2702,11 @@
       <c r="AG22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH22" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2747,8 +2806,11 @@
       <c r="AG23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2848,8 +2910,11 @@
       <c r="AG24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -2949,8 +3014,11 @@
       <c r="AG25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -3050,8 +3118,11 @@
       <c r="AG26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3151,8 +3222,11 @@
       <c r="AG27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3252,8 +3326,11 @@
       <c r="AG28" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3353,8 +3430,11 @@
       <c r="AG29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3454,8 +3534,11 @@
       <c r="AG30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3555,8 +3638,11 @@
       <c r="AG31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3656,8 +3742,11 @@
       <c r="AG32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3757,8 +3846,11 @@
       <c r="AG33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3858,8 +3950,11 @@
       <c r="AG34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -3959,8 +4054,11 @@
       <c r="AG35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -4060,8 +4158,11 @@
       <c r="AG36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="AH36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -4159,6 +4260,9 @@
         <v>3</v>
       </c>
       <c r="AG37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{677DEAD8-939E-4471-840F-C1E452BEB3EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1C3162-4FF4-4744-8F71-5C6F136FCD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="46">
   <si>
     <t>Alunos</t>
   </si>
@@ -161,6 +161,9 @@
   </si>
   <si>
     <t>5/P</t>
+  </si>
+  <si>
+    <t>P/05</t>
   </si>
 </sst>
 </file>
@@ -3327,7 +3330,7 @@
         <v>3</v>
       </c>
       <c r="AH28" s="1" t="s">
-        <v>4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:34" x14ac:dyDescent="0.25">

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF1C3162-4FF4-4744-8F71-5C6F136FCD7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E952B73B-49BC-4D4C-9D90-6CABC8C635C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="46">
   <si>
     <t>Alunos</t>
   </si>
@@ -608,7 +608,8 @@
     <col min="27" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="34" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="6.7109375" style="1"/>
+    <col min="35" max="35" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -712,7 +713,9 @@
       <c r="AH1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AI1" s="2"/>
+      <c r="AI1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AJ1" s="2"/>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
@@ -825,6 +828,9 @@
       <c r="AH2" s="2">
         <v>45805</v>
       </c>
+      <c r="AI2" s="2">
+        <v>45811</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -934,6 +940,9 @@
       <c r="AH4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1038,6 +1047,9 @@
       <c r="AH5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1142,6 +1154,9 @@
       <c r="AH6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1246,6 +1261,9 @@
       <c r="AH7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1350,6 +1368,9 @@
       <c r="AH8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1454,6 +1475,9 @@
       <c r="AH9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1558,6 +1582,9 @@
       <c r="AH10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1662,6 +1689,9 @@
       <c r="AH11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1766,6 +1796,9 @@
       <c r="AH12" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1870,6 +1903,9 @@
       <c r="AH13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -1974,6 +2010,9 @@
       <c r="AH14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -2078,6 +2117,9 @@
       <c r="AH15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AI15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2182,8 +2224,11 @@
       <c r="AH16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2286,8 +2331,11 @@
       <c r="AH17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2390,8 +2438,11 @@
       <c r="AH18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2494,8 +2545,11 @@
       <c r="AH19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2598,14 +2652,17 @@
       <c r="AH20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:34" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AI20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:34" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2708,8 +2765,11 @@
       <c r="AH22" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="23" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2812,8 +2872,11 @@
       <c r="AH23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2916,8 +2979,11 @@
       <c r="AH24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -3020,8 +3086,11 @@
       <c r="AH25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -3124,8 +3193,11 @@
       <c r="AH26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3228,8 +3300,11 @@
       <c r="AH27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3332,8 +3407,11 @@
       <c r="AH28" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="29" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3436,8 +3514,11 @@
       <c r="AH29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3540,8 +3621,11 @@
       <c r="AH30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3644,8 +3728,11 @@
       <c r="AH31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3748,8 +3835,11 @@
       <c r="AH32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3852,8 +3942,11 @@
       <c r="AH33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -3956,8 +4049,11 @@
       <c r="AH34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -4060,8 +4156,11 @@
       <c r="AH35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -4164,8 +4263,11 @@
       <c r="AH36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:34" x14ac:dyDescent="0.25">
+      <c r="AI36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -4266,6 +4368,9 @@
         <v>3</v>
       </c>
       <c r="AH37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E952B73B-49BC-4D4C-9D90-6CABC8C635C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AD772B-EC76-4CAE-82FD-B6C73E9FB7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1194" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="46">
   <si>
     <t>Alunos</t>
   </si>
@@ -716,7 +716,9 @@
       <c r="AI1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AJ1" s="2"/>
+      <c r="AJ1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AK1" s="2"/>
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
@@ -831,6 +833,9 @@
       <c r="AI2" s="2">
         <v>45811</v>
       </c>
+      <c r="AJ2" s="2">
+        <v>45812</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -943,6 +948,9 @@
       <c r="AI4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1050,6 +1058,9 @@
       <c r="AI5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1157,6 +1168,9 @@
       <c r="AI6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1264,6 +1278,9 @@
       <c r="AI7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1371,6 +1388,9 @@
       <c r="AI8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1478,6 +1498,9 @@
       <c r="AI9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1585,6 +1608,9 @@
       <c r="AI10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ10" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1692,6 +1718,9 @@
       <c r="AI11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1799,6 +1828,9 @@
       <c r="AI12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AJ12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1906,6 +1938,9 @@
       <c r="AI13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -2013,6 +2048,9 @@
       <c r="AI14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -2120,6 +2158,9 @@
       <c r="AI15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AJ15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2227,8 +2268,11 @@
       <c r="AI16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2334,8 +2378,11 @@
       <c r="AI17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2441,8 +2488,11 @@
       <c r="AI18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2548,8 +2598,11 @@
       <c r="AI19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2655,14 +2708,17 @@
       <c r="AI20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:35" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AJ20" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:35" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2768,8 +2824,11 @@
       <c r="AI22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2875,8 +2934,11 @@
       <c r="AI23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -2982,8 +3044,11 @@
       <c r="AI24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -3089,8 +3154,11 @@
       <c r="AI25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -3196,8 +3264,11 @@
       <c r="AI26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3303,8 +3374,11 @@
       <c r="AI27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3410,8 +3484,11 @@
       <c r="AI28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3517,8 +3594,11 @@
       <c r="AI29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3624,8 +3704,11 @@
       <c r="AI30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3731,8 +3814,11 @@
       <c r="AI31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3838,8 +3924,11 @@
       <c r="AI32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -3945,8 +4034,11 @@
       <c r="AI33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -4052,8 +4144,11 @@
       <c r="AI34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -4159,8 +4254,11 @@
       <c r="AI35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -4266,8 +4364,11 @@
       <c r="AI36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="AJ36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -4371,6 +4472,9 @@
         <v>3</v>
       </c>
       <c r="AI37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AJ37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6AD772B-EC76-4CAE-82FD-B6C73E9FB7B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E642461-837D-442E-BC3F-47973AAEEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1609,7 +1609,7 @@
         <v>3</v>
       </c>
       <c r="AJ10" s="1" t="s">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E642461-837D-442E-BC3F-47973AAEEEEC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490A23E2-6A82-42AD-A91C-3DBABB25BD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1228" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="46">
   <si>
     <t>Alunos</t>
   </si>
@@ -609,7 +609,9 @@
     <col min="31" max="31" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="32" max="34" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="6.7109375" style="1"/>
+    <col min="36" max="36" width="6.7109375" style="1"/>
+    <col min="37" max="37" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -719,7 +721,9 @@
       <c r="AJ1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AK1" s="2"/>
+      <c r="AK1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AL1" s="2"/>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
@@ -836,6 +840,9 @@
       <c r="AJ2" s="2">
         <v>45812</v>
       </c>
+      <c r="AK2" s="2">
+        <v>45818</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -951,6 +958,9 @@
       <c r="AJ4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1061,6 +1071,9 @@
       <c r="AJ5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1171,6 +1184,9 @@
       <c r="AJ6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1281,6 +1297,9 @@
       <c r="AJ7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1391,6 +1410,9 @@
       <c r="AJ8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1501,6 +1523,9 @@
       <c r="AJ9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1611,6 +1636,9 @@
       <c r="AJ10" s="1" t="s">
         <v>43</v>
       </c>
+      <c r="AK10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1721,6 +1749,9 @@
       <c r="AJ11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1831,6 +1862,9 @@
       <c r="AJ12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AK12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1941,6 +1975,9 @@
       <c r="AJ13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -2051,6 +2088,9 @@
       <c r="AJ14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -2161,6 +2201,9 @@
       <c r="AJ15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AK15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2271,8 +2314,11 @@
       <c r="AJ16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2381,8 +2427,11 @@
       <c r="AJ17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2491,8 +2540,11 @@
       <c r="AJ18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2601,8 +2653,11 @@
       <c r="AJ19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2711,14 +2766,17 @@
       <c r="AJ20" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:36" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AK20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:37" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2827,8 +2885,11 @@
       <c r="AJ22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -2937,8 +2998,11 @@
       <c r="AJ23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -3047,8 +3111,11 @@
       <c r="AJ24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -3157,8 +3224,11 @@
       <c r="AJ25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -3267,8 +3337,11 @@
       <c r="AJ26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3377,8 +3450,11 @@
       <c r="AJ27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3487,8 +3563,11 @@
       <c r="AJ28" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="29" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK28" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3597,8 +3676,11 @@
       <c r="AJ29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3707,8 +3789,11 @@
       <c r="AJ30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3817,8 +3902,11 @@
       <c r="AJ31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -3927,8 +4015,11 @@
       <c r="AJ32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -4037,8 +4128,11 @@
       <c r="AJ33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -4147,8 +4241,11 @@
       <c r="AJ34" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="35" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK34" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -4257,8 +4354,11 @@
       <c r="AJ35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -4367,8 +4467,11 @@
       <c r="AJ36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:36" x14ac:dyDescent="0.25">
+      <c r="AK36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -4475,6 +4578,9 @@
         <v>3</v>
       </c>
       <c r="AJ37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490A23E2-6A82-42AD-A91C-3DBABB25BD56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48944E8C-73B8-410A-8C11-5BFF3A18CB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1262" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="46">
   <si>
     <t>Alunos</t>
   </si>
@@ -610,8 +610,8 @@
     <col min="32" max="34" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="35" max="35" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="36" max="36" width="6.7109375" style="1"/>
-    <col min="37" max="37" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="6.7109375" style="1"/>
+    <col min="37" max="38" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" x14ac:dyDescent="0.25">
@@ -724,7 +724,9 @@
       <c r="AK1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AL1" s="2"/>
+      <c r="AL1" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="AM1" s="2"/>
       <c r="AN1" s="2"/>
       <c r="AO1" s="2"/>
@@ -843,6 +845,9 @@
       <c r="AK2" s="2">
         <v>45818</v>
       </c>
+      <c r="AL2" s="2">
+        <v>45819</v>
+      </c>
     </row>
     <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -961,6 +966,9 @@
       <c r="AK4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -1074,6 +1082,9 @@
       <c r="AK5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
@@ -1187,6 +1198,9 @@
       <c r="AK6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
@@ -1300,6 +1314,9 @@
       <c r="AK7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -1413,6 +1430,9 @@
       <c r="AK8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
@@ -1526,6 +1546,9 @@
       <c r="AK9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
@@ -1639,6 +1662,9 @@
       <c r="AK10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -1752,6 +1778,9 @@
       <c r="AK11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
@@ -1865,6 +1894,9 @@
       <c r="AK12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AL12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
@@ -1978,6 +2010,9 @@
       <c r="AK13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
@@ -2091,6 +2126,9 @@
       <c r="AK14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -2204,6 +2242,9 @@
       <c r="AK15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AL15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
@@ -2317,8 +2358,11 @@
       <c r="AK16" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="17" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL16" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
         <v>33</v>
       </c>
@@ -2430,8 +2474,11 @@
       <c r="AK17" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="18" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL17" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
         <v>34</v>
       </c>
@@ -2543,8 +2590,11 @@
       <c r="AK18" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL18" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
         <v>35</v>
       </c>
@@ -2656,8 +2706,11 @@
       <c r="AK19" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="20" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL19" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
         <v>41</v>
       </c>
@@ -2769,14 +2822,17 @@
       <c r="AK20" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="1:37" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AL20" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:38" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>37</v>
       </c>
       <c r="F21" s="6"/>
     </row>
-    <row r="22" spans="1:37" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
         <v>5</v>
       </c>
@@ -2888,8 +2944,11 @@
       <c r="AK22" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL22" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>8</v>
       </c>
@@ -3001,8 +3060,11 @@
       <c r="AK23" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL23" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>9</v>
       </c>
@@ -3114,8 +3176,11 @@
       <c r="AK24" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="25" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL24" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>11</v>
       </c>
@@ -3227,8 +3292,11 @@
       <c r="AK25" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="26" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL25" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>12</v>
       </c>
@@ -3340,8 +3408,11 @@
       <c r="AK26" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="27" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL26" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>14</v>
       </c>
@@ -3453,8 +3524,11 @@
       <c r="AK27" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="28" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL27" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>16</v>
       </c>
@@ -3564,10 +3638,13 @@
         <v>4</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="29" spans="1:37" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="AL28" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>18</v>
       </c>
@@ -3679,8 +3756,11 @@
       <c r="AK29" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="30" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL29" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>20</v>
       </c>
@@ -3792,8 +3872,11 @@
       <c r="AK30" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL30" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
         <v>21</v>
       </c>
@@ -3905,8 +3988,11 @@
       <c r="AK31" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="32" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL31" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
         <v>24</v>
       </c>
@@ -4018,8 +4104,11 @@
       <c r="AK32" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="33" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL32" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
         <v>27</v>
       </c>
@@ -4131,8 +4220,11 @@
       <c r="AK33" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="34" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL33" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
         <v>28</v>
       </c>
@@ -4244,8 +4336,11 @@
       <c r="AK34" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL34" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
         <v>29</v>
       </c>
@@ -4357,8 +4452,11 @@
       <c r="AK35" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="36" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL35" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
         <v>32</v>
       </c>
@@ -4470,8 +4568,11 @@
       <c r="AK36" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="37" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="AL36" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
         <v>36</v>
       </c>
@@ -4581,6 +4682,9 @@
         <v>3</v>
       </c>
       <c r="AK37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,25 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48944E8C-73B8-410A-8C11-5BFF3A18CB90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8031A5-3BB1-4B2E-90DB-DB0C8649034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
-    <sheet name="alunos" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1296" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="48">
   <si>
     <t>Alunos</t>
   </si>
@@ -165,6 +175,12 @@
   <si>
     <t>P/05</t>
   </si>
+  <si>
+    <t>RA</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
 </sst>
 </file>
 
@@ -227,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -247,7 +263,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -591,279 +606,289 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AQ37"/>
+  <dimension ref="A1:AR37"/>
   <sheetFormatPr defaultColWidth="6.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="38.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="3.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.7109375" style="1"/>
-    <col min="6" max="10" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="7.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="30" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="34" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="6.7109375" style="1"/>
-    <col min="37" max="38" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="6.7109375" style="1"/>
+    <col min="1" max="1" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.7109375" style="1"/>
+    <col min="7" max="11" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="6.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="27" width="7.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="7.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="7.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="6.7109375" style="1"/>
+    <col min="38" max="39" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="V1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="AM1" s="2"/>
-      <c r="AN1" s="2"/>
+      <c r="AN1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
+      <c r="AR1" s="2"/>
     </row>
-    <row r="2" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>45692</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>45693</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>45699</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>45700</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2">
         <v>45706</v>
       </c>
-      <c r="H2" s="2">
+      <c r="I2" s="2">
         <v>45707</v>
       </c>
-      <c r="I2" s="2">
+      <c r="J2" s="2">
         <v>45713</v>
       </c>
-      <c r="J2" s="2">
+      <c r="K2" s="2">
         <v>45714</v>
       </c>
-      <c r="K2" s="2">
+      <c r="L2" s="2">
         <v>45727</v>
       </c>
-      <c r="L2" s="2">
+      <c r="M2" s="2">
         <v>45728</v>
       </c>
-      <c r="M2" s="2">
+      <c r="N2" s="2">
         <v>45734</v>
       </c>
-      <c r="N2" s="2">
+      <c r="O2" s="2">
         <v>45735</v>
       </c>
-      <c r="O2" s="2">
+      <c r="P2" s="2">
         <v>45741</v>
       </c>
-      <c r="P2" s="2">
+      <c r="Q2" s="2">
         <v>45742</v>
       </c>
-      <c r="Q2" s="2">
+      <c r="R2" s="2">
         <v>45748</v>
       </c>
-      <c r="R2" s="2">
+      <c r="S2" s="2">
         <v>45749</v>
       </c>
-      <c r="S2" s="2">
+      <c r="T2" s="2">
         <v>45755</v>
       </c>
-      <c r="T2" s="2">
+      <c r="U2" s="2">
         <v>45756</v>
       </c>
-      <c r="U2" s="2">
+      <c r="V2" s="2">
         <v>45762</v>
       </c>
-      <c r="V2" s="2">
+      <c r="W2" s="2">
         <v>45763</v>
       </c>
-      <c r="W2" s="2">
+      <c r="X2" s="2">
         <v>45769</v>
       </c>
-      <c r="X2" s="2">
+      <c r="Y2" s="2">
         <v>45770</v>
       </c>
-      <c r="Y2" s="2">
+      <c r="Z2" s="2">
         <v>45776</v>
       </c>
-      <c r="Z2" s="2">
+      <c r="AA2" s="2">
         <v>45777</v>
       </c>
-      <c r="AA2" s="2">
+      <c r="AB2" s="2">
         <v>45783</v>
       </c>
-      <c r="AB2" s="2">
+      <c r="AC2" s="2">
         <v>45784</v>
       </c>
-      <c r="AC2" s="2">
+      <c r="AD2" s="2">
         <v>45790</v>
       </c>
-      <c r="AD2" s="2">
+      <c r="AE2" s="2">
         <v>45791</v>
       </c>
-      <c r="AE2" s="2">
+      <c r="AF2" s="2">
         <v>45797</v>
       </c>
-      <c r="AF2" s="2">
+      <c r="AG2" s="2">
         <v>45798</v>
       </c>
-      <c r="AG2" s="2">
+      <c r="AH2" s="2">
         <v>45804</v>
       </c>
-      <c r="AH2" s="2">
+      <c r="AI2" s="2">
         <v>45805</v>
       </c>
-      <c r="AI2" s="2">
+      <c r="AJ2" s="2">
         <v>45811</v>
       </c>
-      <c r="AJ2" s="2">
+      <c r="AK2" s="2">
         <v>45812</v>
       </c>
-      <c r="AK2" s="2">
+      <c r="AL2" s="2">
         <v>45818</v>
       </c>
-      <c r="AL2" s="2">
+      <c r="AM2" s="2">
         <v>45819</v>
       </c>
+      <c r="AN2" s="2">
+        <v>45825</v>
+      </c>
     </row>
-    <row r="3" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:44" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="5" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>24125990</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1">
+      <c r="C4" s="1">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D4" s="1" t="s">
         <v>3</v>
       </c>
@@ -969,17 +994,23 @@
       <c r="AL4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="5" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>24125969</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="1">
+      <c r="C5" s="1">
         <v>2</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D5" s="1" t="s">
         <v>3</v>
       </c>
@@ -1085,15 +1116,21 @@
       <c r="AL5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>24125978</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1">
-        <v>3</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="1">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -1201,17 +1238,23 @@
       <c r="AL6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM6" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>24125985</v>
+      </c>
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1">
+      <c r="C7" s="1">
         <v>4</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D7" s="1" t="s">
         <v>3</v>
       </c>
@@ -1317,17 +1360,23 @@
       <c r="AL7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM7" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>24125988</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B8" s="1">
+      <c r="C8" s="1">
         <v>5</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D8" s="1" t="s">
         <v>3</v>
       </c>
@@ -1433,17 +1482,23 @@
       <c r="AL8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>24126094</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="1">
+      <c r="C9" s="1">
         <v>6</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D9" s="1" t="s">
         <v>3</v>
       </c>
@@ -1466,13 +1521,13 @@
         <v>3</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N9" s="1" t="s">
         <v>3</v>
@@ -1549,17 +1604,23 @@
       <c r="AL9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>24126007</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="1">
+      <c r="C10" s="1">
         <v>7</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D10" s="1" t="s">
         <v>3</v>
       </c>
@@ -1657,25 +1718,31 @@
         <v>3</v>
       </c>
       <c r="AJ10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK10" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AK10" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AL10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>24125974</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="1">
+      <c r="C11" s="1">
         <v>8</v>
       </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D11" s="1" t="s">
         <v>3</v>
       </c>
@@ -1746,25 +1813,25 @@
         <v>3</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AB11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD11" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF11" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AG11" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH11" s="1" t="s">
         <v>3</v>
@@ -1781,17 +1848,20 @@
       <c r="AL11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="1">
+      <c r="C12" s="1">
         <v>9</v>
       </c>
-      <c r="C12" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1859,17 +1929,17 @@
         <v>3</v>
       </c>
       <c r="Z12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AA12" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AB12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AC12" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AC12" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AD12" s="1" t="s">
         <v>3</v>
       </c>
@@ -1886,7 +1956,7 @@
         <v>3</v>
       </c>
       <c r="AI12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AJ12" s="1" t="s">
         <v>4</v>
@@ -1897,17 +1967,23 @@
       <c r="AL12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AM12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>24125977</v>
+      </c>
+      <c r="B13" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="1">
+      <c r="C13" s="1">
         <v>10</v>
       </c>
-      <c r="C13" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D13" s="1" t="s">
         <v>3</v>
       </c>
@@ -2013,17 +2089,23 @@
       <c r="AL13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>24125991</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="1">
+      <c r="C14" s="1">
         <v>11</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D14" s="1" t="s">
         <v>3</v>
       </c>
@@ -2129,17 +2211,23 @@
       <c r="AL14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM14" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>24125967</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B15" s="1">
+      <c r="C15" s="1">
         <v>12</v>
       </c>
-      <c r="C15" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D15" s="1" t="s">
         <v>3</v>
       </c>
@@ -2245,17 +2333,23 @@
       <c r="AL15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM15" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>24125981</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="B16" s="1">
+      <c r="C16" s="1">
         <v>13</v>
       </c>
-      <c r="C16" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D16" s="1" t="s">
         <v>3</v>
       </c>
@@ -2361,17 +2455,23 @@
       <c r="AL16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM16" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>24126277</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="1">
+      <c r="C17" s="1">
         <v>14</v>
       </c>
-      <c r="C17" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D17" s="1" t="s">
         <v>3</v>
       </c>
@@ -2477,17 +2577,23 @@
       <c r="AL17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM17" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>24125982</v>
+      </c>
+      <c r="B18" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="1">
+      <c r="C18" s="1">
         <v>15</v>
       </c>
-      <c r="C18" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D18" s="1" t="s">
         <v>3</v>
       </c>
@@ -2593,17 +2699,23 @@
       <c r="AL18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>24125986</v>
+      </c>
+      <c r="B19" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="1">
+      <c r="C19" s="1">
         <v>16</v>
       </c>
-      <c r="C19" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D19" s="1" t="s">
         <v>3</v>
       </c>
@@ -2689,11 +2801,11 @@
         <v>3</v>
       </c>
       <c r="AF19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG19" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AG19" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AH19" s="1" t="s">
         <v>3</v>
       </c>
@@ -2709,20 +2821,26 @@
       <c r="AL19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM19" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>24127560</v>
+      </c>
+      <c r="B20" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="1">
+      <c r="C20" s="1">
         <v>17</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E20" s="1" t="s">
         <v>3</v>
       </c>
@@ -2760,20 +2878,20 @@
         <v>3</v>
       </c>
       <c r="Q20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R20" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="S20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="T20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U20" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="V20" s="1" t="s">
         <v>3</v>
       </c>
@@ -2808,40 +2926,46 @@
         <v>3</v>
       </c>
       <c r="AG20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AH20" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AH20" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AI20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AJ20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AK20" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AK20" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AL20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM20" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:38" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:40" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
+    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>24126008</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B22" s="1">
+      <c r="C22" s="1">
         <v>18</v>
       </c>
-      <c r="C22" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D22" s="1" t="s">
         <v>3</v>
       </c>
@@ -2858,11 +2982,11 @@
         <v>3</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="K22" s="1" t="s">
         <v>3</v>
       </c>
@@ -2873,11 +2997,11 @@
         <v>3</v>
       </c>
       <c r="N22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="P22" s="1" t="s">
         <v>3</v>
       </c>
@@ -2891,11 +3015,11 @@
         <v>3</v>
       </c>
       <c r="T22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="U22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="U22" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="V22" s="1" t="s">
         <v>3</v>
       </c>
@@ -2912,11 +3036,11 @@
         <v>3</v>
       </c>
       <c r="AA22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB22" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="AB22" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AC22" s="1" t="s">
         <v>3</v>
       </c>
@@ -2933,11 +3057,11 @@
         <v>3</v>
       </c>
       <c r="AH22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI22" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AI22" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AJ22" s="1" t="s">
         <v>3</v>
       </c>
@@ -2947,28 +3071,34 @@
       <c r="AL22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM22" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>24125996</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B23" s="1">
+      <c r="C23" s="1">
         <v>19</v>
       </c>
-      <c r="C23" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>3</v>
@@ -2995,11 +3125,11 @@
         <v>3</v>
       </c>
       <c r="P23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Q23" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="R23" s="1" t="s">
         <v>3</v>
       </c>
@@ -3019,23 +3149,23 @@
         <v>3</v>
       </c>
       <c r="X23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Y23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="Y23" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="Z23" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AA23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB23" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AB23" s="1" t="s">
+      <c r="AC23" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AC23" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AD23" s="1" t="s">
         <v>3</v>
       </c>
@@ -3063,17 +3193,23 @@
       <c r="AL23" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN23" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
+    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>24125975</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="1">
+      <c r="C24" s="1">
         <v>20</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D24" s="1" t="s">
         <v>3</v>
       </c>
@@ -3179,17 +3315,23 @@
       <c r="AL24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM24" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A25" s="1">
+        <v>24125993</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B25" s="1">
+      <c r="C25" s="1">
         <v>21</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D25" s="1" t="s">
         <v>3</v>
       </c>
@@ -3257,11 +3399,11 @@
         <v>3</v>
       </c>
       <c r="Z25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AA25" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="AA25" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AB25" s="1" t="s">
         <v>3</v>
       </c>
@@ -3295,32 +3437,38 @@
       <c r="AL25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM25" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A26" s="1">
+        <v>24126043</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="1">
+      <c r="C26" s="1">
         <v>22</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>4</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H26" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="I26" s="1" t="s">
         <v>3</v>
       </c>
@@ -3411,17 +3559,23 @@
       <c r="AL26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
+    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A27" s="1">
+        <v>24125984</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B27" s="1">
+      <c r="C27" s="1">
         <v>23</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D27" s="1" t="s">
         <v>3</v>
       </c>
@@ -3527,17 +3681,23 @@
       <c r="AL27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM27" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN27" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A28" s="1">
+        <v>24126459</v>
+      </c>
+      <c r="B28" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B28" s="1">
+      <c r="C28" s="1">
         <v>24</v>
       </c>
-      <c r="C28" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D28" s="1" t="s">
         <v>3</v>
       </c>
@@ -3548,11 +3708,11 @@
         <v>3</v>
       </c>
       <c r="G28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="H28" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="I28" s="1" t="s">
         <v>3</v>
       </c>
@@ -3611,7 +3771,7 @@
         <v>3</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC28" s="1" t="s">
         <v>4</v>
@@ -3620,7 +3780,7 @@
         <v>4</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF28" s="1" t="s">
         <v>3</v>
@@ -3629,34 +3789,40 @@
         <v>3</v>
       </c>
       <c r="AH28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AI28" s="1" t="s">
         <v>45</v>
-      </c>
-      <c r="AI28" s="1" t="s">
-        <v>4</v>
       </c>
       <c r="AJ28" s="1" t="s">
         <v>4</v>
       </c>
       <c r="AK28" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL28" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN28" s="1" t="s">
+        <v>47</v>
+      </c>
     </row>
-    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A29" s="1">
+        <v>24126041</v>
+      </c>
+      <c r="B29" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="B29" s="1">
+      <c r="C29" s="1">
         <v>25</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D29" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="E29" s="1" t="s">
         <v>3</v>
       </c>
@@ -3700,11 +3866,11 @@
         <v>3</v>
       </c>
       <c r="S29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T29" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T29" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="U29" s="1" t="s">
         <v>3</v>
       </c>
@@ -3759,17 +3925,23 @@
       <c r="AL29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A30" s="1">
+        <v>24126396</v>
+      </c>
+      <c r="B30" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B30" s="1">
+      <c r="C30" s="1">
         <v>26</v>
       </c>
-      <c r="C30" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D30" s="1" t="s">
         <v>3</v>
       </c>
@@ -3801,11 +3973,11 @@
         <v>3</v>
       </c>
       <c r="N30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="O30" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="P30" s="1" t="s">
         <v>3</v>
       </c>
@@ -3875,17 +4047,23 @@
       <c r="AL30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM30" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A31" s="1">
+        <v>24125987</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="1">
+      <c r="C31" s="1">
         <v>27</v>
       </c>
-      <c r="C31" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D31" s="1" t="s">
         <v>3</v>
       </c>
@@ -3991,23 +4169,29 @@
       <c r="AL31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM31" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A32" s="1">
+        <v>24125992</v>
+      </c>
+      <c r="B32" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B32" s="1">
+      <c r="C32" s="1">
         <v>28</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="E32" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E32" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="F32" s="1" t="s">
         <v>3</v>
       </c>
@@ -4107,17 +4291,23 @@
       <c r="AL32" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN32" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A33" s="1">
+        <v>24125989</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B33" s="1">
+      <c r="C33" s="1">
         <v>29</v>
       </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D33" s="1" t="s">
         <v>3</v>
       </c>
@@ -4223,17 +4413,23 @@
       <c r="AL33" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM33" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN33" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
+    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A34" s="1">
+        <v>24125983</v>
+      </c>
+      <c r="B34" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B34" s="1">
+      <c r="C34" s="1">
         <v>30</v>
       </c>
-      <c r="C34" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D34" s="1" t="s">
         <v>3</v>
       </c>
@@ -4298,11 +4494,11 @@
         <v>3</v>
       </c>
       <c r="Y34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="Z34" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Z34" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="AA34" s="1" t="s">
         <v>3</v>
       </c>
@@ -4334,22 +4530,28 @@
         <v>3</v>
       </c>
       <c r="AK34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AL34" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="AL34" s="1" t="s">
+      <c r="AM34" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN34" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A35" s="1">
+        <v>24125976</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="1">
+      <c r="C35" s="1">
         <v>31</v>
       </c>
-      <c r="C35" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D35" s="1" t="s">
         <v>3</v>
       </c>
@@ -4455,17 +4657,23 @@
       <c r="AL35" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM35" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN35" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A36" s="4" t="s">
+    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A36" s="1">
+        <v>24126030</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B36" s="1">
+      <c r="C36" s="1">
         <v>32</v>
       </c>
-      <c r="C36" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D36" s="1" t="s">
         <v>3</v>
       </c>
@@ -4571,17 +4779,23 @@
       <c r="AL36" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AM36" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN36" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
+    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+      <c r="A37" s="1">
+        <v>24125994</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B37" s="1">
+      <c r="C37" s="1">
         <v>33</v>
       </c>
-      <c r="C37" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="D37" s="1" t="s">
         <v>3</v>
       </c>
@@ -4601,11 +4815,11 @@
         <v>3</v>
       </c>
       <c r="J37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="K37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K37" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="L37" s="1" t="s">
         <v>3</v>
       </c>
@@ -4622,17 +4836,17 @@
         <v>3</v>
       </c>
       <c r="Q37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="R37" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="R37" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="S37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="T37" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="T37" s="1" t="s">
-        <v>3</v>
-      </c>
       <c r="U37" s="1" t="s">
         <v>3</v>
       </c>
@@ -4685,18 +4899,24 @@
         <v>3</v>
       </c>
       <c r="AL37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AM37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AN37" s="1" t="s">
         <v>3</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A22:A37">
-    <sortCondition ref="A22:A37"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B22:B37">
+    <sortCondition ref="B22:B37"/>
   </sortState>
   <mergeCells count="1">
-    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="A1:XFD1048576">
+  <conditionalFormatting sqref="D1:XFD1 A1 A2:XFD1048576">
     <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4704,7 +4924,7 @@
       <formula>"F"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="O34:O37">
+  <conditionalFormatting sqref="P34:P37">
     <cfRule type="cellIs" dxfId="0" priority="7" operator="equal">
       <formula>"F"</formula>
     </cfRule>
@@ -4712,191 +4932,4 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5601EA4F-B083-49FB-A81E-FB069AE1076F}">
-  <dimension ref="A1:A34"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="36.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>36</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A34">
-    <sortCondition ref="A1:A34"/>
-  </sortState>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F8031A5-3BB1-4B2E-90DB-DB0C8649034F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0B4A6E-C2B9-426B-80EF-E07FE306765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -72,9 +72,6 @@
   </si>
   <si>
     <t>Evelyn Fernandes</t>
-  </si>
-  <si>
-    <t>Femando Joaquim Mota</t>
   </si>
   <si>
     <t>Hélio Alves de Oliveira</t>
@@ -181,6 +178,9 @@
   <si>
     <t>p</t>
   </si>
+  <si>
+    <t>Fernando Joaquim Mota</t>
+  </si>
 </sst>
 </file>
 
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -265,6 +265,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -637,115 +640,115 @@
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
       <c r="D1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="F1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="H1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="K1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="L1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="N1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="P1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="R1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="S1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="S1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="T1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="U1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="V1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="W1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="W1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="X1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="Y1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="Z1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AA1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AA1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AB1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AC1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AC1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AD1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AE1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AF1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AG1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AG1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AH1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AI1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AI1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AJ1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AK1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AK1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AL1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AM1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AM1" s="2" t="s">
-        <v>40</v>
-      </c>
       <c r="AN1" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AO1" s="2"/>
       <c r="AP1" s="2"/>
@@ -754,7 +757,7 @@
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>1</v>
@@ -876,7 +879,7 @@
     </row>
     <row r="3" spans="1:44" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:44" x14ac:dyDescent="0.25">
@@ -1250,7 +1253,7 @@
         <v>24125985</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C7" s="1">
         <v>4</v>
@@ -1372,7 +1375,7 @@
         <v>24125988</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8" s="1">
         <v>5</v>
@@ -1494,7 +1497,7 @@
         <v>24126094</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1">
         <v>6</v>
@@ -1616,7 +1619,7 @@
         <v>24126007</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1">
         <v>7</v>
@@ -1721,7 +1724,7 @@
         <v>3</v>
       </c>
       <c r="AK10" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AL10" s="1" t="s">
         <v>3</v>
@@ -1738,7 +1741,7 @@
         <v>24125974</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" s="1">
         <v>8</v>
@@ -1857,7 +1860,7 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C12" s="1">
         <v>9</v>
@@ -1932,13 +1935,13 @@
         <v>3</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AB12" s="1" t="s">
         <v>3</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AD12" s="1" t="s">
         <v>3</v>
@@ -1979,7 +1982,7 @@
         <v>24125977</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1">
         <v>10</v>
@@ -2101,7 +2104,7 @@
         <v>24125991</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1">
         <v>11</v>
@@ -2223,7 +2226,7 @@
         <v>24125967</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C15" s="1">
         <v>12</v>
@@ -2345,7 +2348,7 @@
         <v>24125981</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C16" s="1">
         <v>13</v>
@@ -2467,7 +2470,7 @@
         <v>24126277</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1">
         <v>14</v>
@@ -2589,7 +2592,7 @@
         <v>24125982</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="1">
         <v>15</v>
@@ -2711,7 +2714,7 @@
         <v>24125986</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="1">
         <v>16</v>
@@ -2833,7 +2836,7 @@
         <v>24127560</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C20" s="1">
         <v>17</v>
@@ -2929,7 +2932,7 @@
         <v>3</v>
       </c>
       <c r="AH20" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AI20" s="1" t="s">
         <v>3</v>
@@ -2952,7 +2955,7 @@
     </row>
     <row r="21" spans="1:40" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G21" s="6"/>
     </row>
@@ -3039,7 +3042,7 @@
         <v>3</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AC22" s="1" t="s">
         <v>3</v>
@@ -3161,7 +3164,7 @@
         <v>3</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AC23" s="1" t="s">
         <v>4</v>
@@ -3402,7 +3405,7 @@
         <v>3</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AB25" s="1" t="s">
         <v>3</v>
@@ -3448,8 +3451,8 @@
       <c r="A26" s="1">
         <v>24126043</v>
       </c>
-      <c r="B26" s="4" t="s">
-        <v>12</v>
+      <c r="B26" s="8" t="s">
+        <v>47</v>
       </c>
       <c r="C26" s="1">
         <v>22</v>
@@ -3571,7 +3574,7 @@
         <v>24125984</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C27" s="1">
         <v>23</v>
@@ -3693,7 +3696,7 @@
         <v>24126459</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>24</v>
@@ -3711,7 +3714,7 @@
         <v>3</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>3</v>
@@ -3792,7 +3795,7 @@
         <v>3</v>
       </c>
       <c r="AI28" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AJ28" s="1" t="s">
         <v>4</v>
@@ -3807,7 +3810,7 @@
         <v>3</v>
       </c>
       <c r="AN28" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.25">
@@ -3815,7 +3818,7 @@
         <v>24126041</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="1">
         <v>25</v>
@@ -3869,7 +3872,7 @@
         <v>3</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U29" s="1" t="s">
         <v>3</v>
@@ -3937,7 +3940,7 @@
         <v>24126396</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C30" s="1">
         <v>26</v>
@@ -4059,7 +4062,7 @@
         <v>24125987</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C31" s="1">
         <v>27</v>
@@ -4181,7 +4184,7 @@
         <v>24125992</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C32" s="1">
         <v>28</v>
@@ -4190,7 +4193,7 @@
         <v>4</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>3</v>
@@ -4303,7 +4306,7 @@
         <v>24125989</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C33" s="1">
         <v>29</v>
@@ -4425,7 +4428,7 @@
         <v>24125983</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C34" s="1">
         <v>30</v>
@@ -4497,7 +4500,7 @@
         <v>3</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AA34" s="1" t="s">
         <v>3</v>
@@ -4547,7 +4550,7 @@
         <v>24125976</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C35" s="1">
         <v>31</v>
@@ -4669,7 +4672,7 @@
         <v>24126030</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C36" s="1">
         <v>32</v>
@@ -4791,7 +4794,7 @@
         <v>24125994</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C37" s="1">
         <v>33</v>
@@ -4845,7 +4848,7 @@
         <v>3</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="U37" s="1" t="s">
         <v>3</v>
@@ -4916,7 +4919,7 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
-  <conditionalFormatting sqref="D1:XFD1 A1 A2:XFD1048576">
+  <conditionalFormatting sqref="A1 D1:XFD1 A2:XFD1048576">
     <cfRule type="cellIs" dxfId="2" priority="6" operator="equal">
       <formula>"F"</formula>
     </cfRule>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B0B4A6E-C2B9-426B-80EF-E07FE306765C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6307F7-E995-497E-B7D8-30A9D2FFAECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1297" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="48">
   <si>
     <t>Alunos</t>
   </si>
@@ -266,7 +266,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -630,7 +630,9 @@
     <col min="36" max="36" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="37" max="37" width="6.7109375" style="1"/>
     <col min="38" max="39" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="16384" width="6.7109375" style="1"/>
+    <col min="40" max="40" width="6.7109375" style="1"/>
+    <col min="41" max="41" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.25">
@@ -750,7 +752,9 @@
       <c r="AN1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="AO1" s="2"/>
+      <c r="AO1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AP1" s="2"/>
       <c r="AQ1" s="2"/>
       <c r="AR1" s="2"/>
@@ -876,6 +880,9 @@
       <c r="AN2" s="2">
         <v>45825</v>
       </c>
+      <c r="AO2" s="2">
+        <v>45826</v>
+      </c>
     </row>
     <row r="3" spans="1:44" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
@@ -1003,6 +1010,9 @@
       <c r="AN4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1125,6 +1135,9 @@
       <c r="AN5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1247,6 +1260,9 @@
       <c r="AN6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1369,6 +1385,9 @@
       <c r="AN7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1491,6 +1510,9 @@
       <c r="AN8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1613,6 +1635,9 @@
       <c r="AN9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1735,6 +1760,9 @@
       <c r="AN10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1857,6 +1885,9 @@
       <c r="AN11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -1976,6 +2007,9 @@
       <c r="AN12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AO12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2098,6 +2132,9 @@
       <c r="AN13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2220,6 +2257,9 @@
       <c r="AN14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2342,6 +2382,9 @@
       <c r="AN15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -2464,8 +2507,11 @@
       <c r="AN16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126277</v>
       </c>
@@ -2586,8 +2632,11 @@
       <c r="AN17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24125982</v>
       </c>
@@ -2708,8 +2757,11 @@
       <c r="AN18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24125986</v>
       </c>
@@ -2830,8 +2882,11 @@
       <c r="AN19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="20" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24127560</v>
       </c>
@@ -2952,14 +3007,17 @@
       <c r="AN20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:40" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24126008</v>
       </c>
@@ -3080,8 +3138,11 @@
       <c r="AN22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125996</v>
       </c>
@@ -3202,8 +3263,11 @@
       <c r="AN23" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AO23" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="24" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125975</v>
       </c>
@@ -3324,8 +3388,11 @@
       <c r="AN24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125993</v>
       </c>
@@ -3446,8 +3513,11 @@
       <c r="AN25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24126043</v>
       </c>
@@ -3568,8 +3638,11 @@
       <c r="AN26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125984</v>
       </c>
@@ -3690,8 +3763,11 @@
       <c r="AN27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO27" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24126459</v>
       </c>
@@ -3812,8 +3888,11 @@
       <c r="AN28" s="1" t="s">
         <v>46</v>
       </c>
+      <c r="AO28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24126041</v>
       </c>
@@ -3934,8 +4013,11 @@
       <c r="AN29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126396</v>
       </c>
@@ -4056,8 +4138,11 @@
       <c r="AN30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24125987</v>
       </c>
@@ -4178,8 +4263,11 @@
       <c r="AN31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125992</v>
       </c>
@@ -4300,8 +4388,11 @@
       <c r="AN32" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO32" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125989</v>
       </c>
@@ -4422,8 +4513,11 @@
       <c r="AN33" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO33" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125983</v>
       </c>
@@ -4544,8 +4638,11 @@
       <c r="AN34" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO34" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="35" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>24125976</v>
       </c>
@@ -4666,8 +4763,11 @@
       <c r="AN35" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO35" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>24126030</v>
       </c>
@@ -4788,8 +4888,11 @@
       <c r="AN36" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AO36" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="1:40" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>24125994</v>
       </c>
@@ -4908,6 +5011,9 @@
         <v>3</v>
       </c>
       <c r="AN37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AO37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6307F7-E995-497E-B7D8-30A9D2FFAECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A41610-D987-4864-90D8-68502F69590C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -265,9 +265,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3521,7 +3518,7 @@
       <c r="A26" s="1">
         <v>24126043</v>
       </c>
-      <c r="B26" s="8" t="s">
+      <c r="B26" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="1">

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21A41610-D987-4864-90D8-68502F69590C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7156F4-4715-4383-8E99-EDF56B3BDE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1331" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="48">
   <si>
     <t>Alunos</t>
   </si>
@@ -628,8 +628,8 @@
     <col min="37" max="37" width="6.7109375" style="1"/>
     <col min="38" max="39" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="40" max="40" width="6.7109375" style="1"/>
-    <col min="41" max="41" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="6.7109375" style="1"/>
+    <col min="41" max="42" width="6.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="6.7109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:44" x14ac:dyDescent="0.25">
@@ -752,8 +752,12 @@
       <c r="AO1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="AP1" s="2"/>
-      <c r="AQ1" s="2"/>
+      <c r="AP1" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="AQ1" s="2" t="s">
+        <v>39</v>
+      </c>
       <c r="AR1" s="2"/>
     </row>
     <row r="2" spans="1:44" x14ac:dyDescent="0.25">
@@ -880,6 +884,12 @@
       <c r="AO2" s="2">
         <v>45826</v>
       </c>
+      <c r="AP2" s="2">
+        <v>45832</v>
+      </c>
+      <c r="AQ2" s="2">
+        <v>45833</v>
+      </c>
     </row>
     <row r="3" spans="1:44" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="5" t="s">
@@ -1010,6 +1020,9 @@
       <c r="AO4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1135,6 +1148,9 @@
       <c r="AO5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1260,6 +1276,9 @@
       <c r="AO6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1385,6 +1404,9 @@
       <c r="AO7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1510,6 +1532,9 @@
       <c r="AO8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1635,6 +1660,9 @@
       <c r="AO9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1760,6 +1788,9 @@
       <c r="AO10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1885,6 +1916,9 @@
       <c r="AO11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -2007,6 +2041,9 @@
       <c r="AO12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AP12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2132,6 +2169,9 @@
       <c r="AO13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2257,6 +2297,9 @@
       <c r="AO14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2382,6 +2425,9 @@
       <c r="AO15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -2507,8 +2553,11 @@
       <c r="AO16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126277</v>
       </c>
@@ -2632,8 +2681,11 @@
       <c r="AO17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24125982</v>
       </c>
@@ -2757,8 +2809,11 @@
       <c r="AO18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24125986</v>
       </c>
@@ -2882,8 +2937,11 @@
       <c r="AO19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24127560</v>
       </c>
@@ -3007,14 +3065,17 @@
       <c r="AO20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:41" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24126008</v>
       </c>
@@ -3138,8 +3199,11 @@
       <c r="AO22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125996</v>
       </c>
@@ -3263,8 +3327,11 @@
       <c r="AO23" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AP23" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125975</v>
       </c>
@@ -3388,8 +3455,11 @@
       <c r="AO24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125993</v>
       </c>
@@ -3513,8 +3583,11 @@
       <c r="AO25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24126043</v>
       </c>
@@ -3638,8 +3711,11 @@
       <c r="AO26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125984</v>
       </c>
@@ -3763,8 +3839,11 @@
       <c r="AO27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP27" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24126459</v>
       </c>
@@ -3888,8 +3967,11 @@
       <c r="AO28" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24126041</v>
       </c>
@@ -4013,8 +4095,11 @@
       <c r="AO29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126396</v>
       </c>
@@ -4138,8 +4223,11 @@
       <c r="AO30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24125987</v>
       </c>
@@ -4263,8 +4351,11 @@
       <c r="AO31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125992</v>
       </c>
@@ -4388,8 +4479,11 @@
       <c r="AO32" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP32" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125989</v>
       </c>
@@ -4513,8 +4607,11 @@
       <c r="AO33" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP33" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125983</v>
       </c>
@@ -4638,8 +4735,11 @@
       <c r="AO34" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP34" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>24125976</v>
       </c>
@@ -4763,8 +4863,11 @@
       <c r="AO35" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP35" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>24126030</v>
       </c>
@@ -4888,8 +4991,11 @@
       <c r="AO36" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AP36" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>24125994</v>
       </c>
@@ -5011,6 +5117,9 @@
         <v>3</v>
       </c>
       <c r="AO37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AP37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7156F4-4715-4383-8E99-EDF56B3BDE0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA4C499-A38D-452B-84BE-D73A93A8A220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6180" yWindow="1020" windowWidth="13875" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1399" uniqueCount="48">
   <si>
     <t>Alunos</t>
   </si>
@@ -1023,6 +1023,9 @@
       <c r="AP4" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ4" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -1151,6 +1154,9 @@
       <c r="AP5" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ5" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1279,6 +1285,9 @@
       <c r="AP6" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ6" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1407,6 +1416,9 @@
       <c r="AP7" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ7" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1535,6 +1547,9 @@
       <c r="AP8" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ8" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1663,6 +1678,9 @@
       <c r="AP9" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ9" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1791,6 +1809,9 @@
       <c r="AP10" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ10" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1919,6 +1940,9 @@
       <c r="AP11" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ11" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.25">
       <c r="B12" s="4" t="s">
@@ -2044,6 +2068,9 @@
       <c r="AP12" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="AQ12" s="1" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2172,6 +2199,9 @@
       <c r="AP13" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ13" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -2300,6 +2330,9 @@
       <c r="AP14" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ14" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -2428,6 +2461,9 @@
       <c r="AP15" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ15" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="16" spans="1:44" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -2556,8 +2592,11 @@
       <c r="AP16" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ16" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
         <v>24126277</v>
       </c>
@@ -2684,8 +2723,11 @@
       <c r="AP17" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ17" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
         <v>24125982</v>
       </c>
@@ -2812,8 +2854,11 @@
       <c r="AP18" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ18" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
         <v>24125986</v>
       </c>
@@ -2940,8 +2985,11 @@
       <c r="AP19" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ19" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
         <v>24127560</v>
       </c>
@@ -3068,14 +3116,17 @@
       <c r="AP20" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ20" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="21" spans="1:42" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>36</v>
       </c>
       <c r="G21" s="6"/>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
         <v>24126008</v>
       </c>
@@ -3202,8 +3253,11 @@
       <c r="AP22" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ22" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
         <v>24125996</v>
       </c>
@@ -3330,8 +3384,11 @@
       <c r="AP23" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ23" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>24125975</v>
       </c>
@@ -3458,8 +3515,11 @@
       <c r="AP24" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ24" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
         <v>24125993</v>
       </c>
@@ -3586,8 +3646,11 @@
       <c r="AP25" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ25" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
         <v>24126043</v>
       </c>
@@ -3714,8 +3777,11 @@
       <c r="AP26" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ26" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
         <v>24125984</v>
       </c>
@@ -3842,8 +3908,11 @@
       <c r="AP27" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ27" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
         <v>24126459</v>
       </c>
@@ -3970,8 +4039,11 @@
       <c r="AP28" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ28" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
         <v>24126041</v>
       </c>
@@ -4098,8 +4170,11 @@
       <c r="AP29" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ29" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
         <v>24126396</v>
       </c>
@@ -4226,8 +4301,11 @@
       <c r="AP30" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ30" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
         <v>24125987</v>
       </c>
@@ -4354,8 +4432,11 @@
       <c r="AP31" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ31" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>24125992</v>
       </c>
@@ -4482,8 +4563,11 @@
       <c r="AP32" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ32" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
         <v>24125989</v>
       </c>
@@ -4610,8 +4694,11 @@
       <c r="AP33" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ33" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A34" s="1">
         <v>24125983</v>
       </c>
@@ -4738,8 +4825,11 @@
       <c r="AP34" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ34" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
         <v>24125976</v>
       </c>
@@ -4866,8 +4956,11 @@
       <c r="AP35" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ35" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A36" s="1">
         <v>24126030</v>
       </c>
@@ -4994,8 +5087,11 @@
       <c r="AP36" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="AQ36" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
         <v>24125994</v>
       </c>
@@ -5120,6 +5216,9 @@
         <v>3</v>
       </c>
       <c r="AP37" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="AQ37" s="1" t="s">
         <v>3</v>
       </c>
     </row>

--- a/ds/3des/frequencia.xlsx
+++ b/ds/3des/frequencia.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\wellifabio\senai2025\ds\3des\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FA4C499-A38D-452B-84BE-D73A93A8A220}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5126E5A-1722-4EAA-BC7D-7AF515644C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6180" yWindow="1020" windowWidth="13875" windowHeight="14460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chamada" sheetId="1" r:id="rId1"/>
